--- a/output/2026-10-12/enriched_analysis.xlsx
+++ b/output/2026-10-12/enriched_analysis.xlsx
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>2.266</v>
+        <v>2.253</v>
       </c>
       <c r="W2" t="n">
-        <v>2780</v>
+        <v>2796</v>
       </c>
       <c r="X2" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="Y2" t="n">
         <v>75</v>
@@ -1161,13 +1161,13 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>0.885</v>
+        <v>0.878</v>
       </c>
       <c r="W3" t="n">
-        <v>915</v>
+        <v>922</v>
       </c>
       <c r="X3" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Y3" t="n">
         <v>47</v>
@@ -1393,13 +1393,13 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>0.046</v>
+        <v>0.044</v>
       </c>
       <c r="W4" t="n">
-        <v>2903</v>
+        <v>3016</v>
       </c>
       <c r="X4" t="n">
-        <v>9.98</v>
+        <v>10.4</v>
       </c>
       <c r="Y4" t="n">
         <v>36</v>
@@ -1625,10 +1625,10 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>1.867</v>
+        <v>1.93</v>
       </c>
       <c r="W5" t="n">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
@@ -1855,13 +1855,13 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>1.115</v>
+        <v>1.173</v>
       </c>
       <c r="W6" t="n">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="X6" t="n">
-        <v>7.64</v>
+        <v>7.24</v>
       </c>
       <c r="Y6" t="n">
         <v>17</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>1.188</v>
+        <v>1.199</v>
       </c>
       <c r="W7" t="n">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="X7" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="Y7" t="n">
         <v>22</v>
@@ -2322,10 +2322,10 @@
         <v>0.047</v>
       </c>
       <c r="W8" t="n">
-        <v>15198</v>
+        <v>15182</v>
       </c>
       <c r="X8" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="Y8" t="n">
         <v>83</v>
@@ -2551,13 +2551,13 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>0.576</v>
+        <v>0.528</v>
       </c>
       <c r="W9" t="n">
-        <v>503</v>
+        <v>549</v>
       </c>
       <c r="X9" t="n">
-        <v>12.6</v>
+        <v>13.8</v>
       </c>
       <c r="Y9" t="n">
         <v>19</v>
@@ -2783,13 +2783,13 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>2.338</v>
+        <v>2.362</v>
       </c>
       <c r="W10" t="n">
-        <v>2511</v>
+        <v>2485</v>
       </c>
       <c r="X10" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="Y10" t="n">
         <v>6</v>
@@ -3021,7 +3021,7 @@
         <v>916</v>
       </c>
       <c r="X11" t="n">
-        <v>9.01</v>
+        <v>8.98</v>
       </c>
       <c r="Y11" t="n">
         <v>7</v>
@@ -3247,13 +3247,13 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>0.052</v>
+        <v>0.05</v>
       </c>
       <c r="W12" t="n">
-        <v>1593</v>
+        <v>1654</v>
       </c>
       <c r="X12" t="n">
-        <v>21.4</v>
+        <v>22.3</v>
       </c>
       <c r="Y12" t="n">
         <v>55</v>
@@ -3482,10 +3482,10 @@
         <v>0.066</v>
       </c>
       <c r="W13" t="n">
-        <v>853</v>
+        <v>860</v>
       </c>
       <c r="X13" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="Y13" t="n">
         <v>19</v>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>2549</v>
+        <v>2552</v>
       </c>
       <c r="X14" t="n">
         <v>20.9</v>
@@ -3941,10 +3941,10 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>0.13</v>
+        <v>0.131</v>
       </c>
       <c r="W15" t="n">
-        <v>2412</v>
+        <v>2401</v>
       </c>
       <c r="X15" t="n">
         <v>21.1</v>
@@ -4176,10 +4176,10 @@
         <v>0.067</v>
       </c>
       <c r="W16" t="n">
-        <v>1663</v>
+        <v>1642</v>
       </c>
       <c r="X16" t="n">
-        <v>38.2</v>
+        <v>37.7</v>
       </c>
       <c r="Y16" t="n">
         <v>20</v>
@@ -4405,13 +4405,13 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>0.301</v>
+        <v>0.318</v>
       </c>
       <c r="W17" t="n">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="X17" t="n">
-        <v>25.5</v>
+        <v>24.1</v>
       </c>
       <c r="Y17" t="n">
         <v>12</v>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>3.014</v>
+        <v>3.051</v>
       </c>
       <c r="W18" t="n">
-        <v>653</v>
+        <v>645</v>
       </c>
       <c r="X18" t="n">
-        <v>19.7</v>
+        <v>19.5</v>
       </c>
       <c r="Y18" t="n">
         <v>30</v>
@@ -4863,13 +4863,13 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>0.187</v>
+        <v>0.18</v>
       </c>
       <c r="W19" t="n">
-        <v>594</v>
+        <v>617</v>
       </c>
       <c r="X19" t="n">
-        <v>49.6</v>
+        <v>51.5</v>
       </c>
       <c r="Y19" t="n">
         <v>3</v>
@@ -5098,10 +5098,10 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>55024</v>
+        <v>54686</v>
       </c>
       <c r="X20" t="n">
-        <v>46.6</v>
+        <v>46.4</v>
       </c>
       <c r="Y20" t="n">
         <v>5</v>
@@ -5255,12 +5255,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HTEL</t>
+          <t>JAYAGROGN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers Limited</t>
+          <t>Jayant Agro-Organics Limited</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -5272,101 +5272,107 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="G21" t="n">
+        <v>13</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>212.86</v>
+      </c>
+      <c r="J21" t="n">
+        <v>232.74</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="L21" t="n">
+        <v>67.13</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="N21" t="n">
+        <v>5704863</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>5704863</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
         <v>4</v>
       </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>90.37</v>
-      </c>
-      <c r="J21" t="n">
-        <v>68.68000000000001</v>
-      </c>
-      <c r="K21" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="L21" t="n">
-        <v>71.22</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="N21" t="n">
-        <v>8585000</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>8585000</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S21" t="b">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>24-09-2026</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="W21" t="n">
+        <v>633</v>
+      </c>
+      <c r="X21" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA21" t="n">
         <v>1</v>
       </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>29-09-2026</t>
-        </is>
-      </c>
-      <c r="V21" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="W21" t="n">
-        <v>857</v>
-      </c>
-      <c r="X21" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>8.44</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>39</v>
-      </c>
       <c r="AB21" t="n">
-        <v>0.55</v>
+        <v>6.54</v>
       </c>
       <c r="AC21" t="n">
-        <v>23.9</v>
+        <v>14.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
       <c r="AE21" t="b">
         <v>1</v>
       </c>
       <c r="AF21" t="n">
-        <v>19.61</v>
-      </c>
-      <c r="AG21" t="inlineStr"/>
-      <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>226.38</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>205.68</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>10.8</v>
+      </c>
       <c r="AJ21" t="n">
-        <v>68.68000000000001</v>
+        <v>232.7375571148825</v>
       </c>
       <c r="AK21" t="n">
-        <v>31.6</v>
+        <v>-8.5</v>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
@@ -5375,62 +5381,62 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AR21" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AS21" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AT21" t="n">
         <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AW21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AX21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AY21" t="n">
         <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>8585000</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>8585000</v>
+        <v>5704863</v>
       </c>
       <c r="BB21" t="n">
-        <v>8585000</v>
+        <v>5704863</v>
       </c>
       <c r="BC21" t="n">
-        <v>8585000</v>
+        <v>5704863</v>
       </c>
       <c r="BD21" t="n">
         <v>0</v>
@@ -5466,7 +5472,7 @@
         <v>0</v>
       </c>
       <c r="BO21" t="n">
-        <v>8585000</v>
+        <v>5704863</v>
       </c>
       <c r="BP21" t="n">
         <v>1</v>
@@ -5481,16 +5487,16 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JAYAGROGN</t>
+          <t>HTEL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jayant Agro-Organics Limited</t>
+          <t>Hy-Tech Engineers Limited</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5501,37 +5507,37 @@
         <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="G22" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>212.86</v>
+        <v>90.37</v>
       </c>
       <c r="J22" t="n">
-        <v>232.74</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>-8.5</v>
+        <v>31.6</v>
       </c>
       <c r="L22" t="n">
-        <v>67.13</v>
+        <v>71.22</v>
       </c>
       <c r="M22" t="n">
-        <v>0.57</v>
+        <v>0.86</v>
       </c>
       <c r="N22" t="n">
-        <v>5704863</v>
+        <v>8585000</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>5704863</v>
+        <v>8585000</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -5545,60 +5551,54 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="V22" t="n">
-        <v>0.089</v>
+        <v>0.099</v>
       </c>
       <c r="W22" t="n">
-        <v>639</v>
+        <v>871</v>
       </c>
       <c r="X22" t="n">
-        <v>10.4</v>
+        <v>38</v>
       </c>
       <c r="Y22" t="n">
-        <v>-5</v>
+        <v>17</v>
       </c>
       <c r="Z22" t="n">
-        <v>32</v>
+        <v>8.44</v>
       </c>
       <c r="AA22" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="AB22" t="n">
-        <v>6.54</v>
+        <v>0.55</v>
       </c>
       <c r="AC22" t="n">
-        <v>14.8</v>
+        <v>23.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.11</v>
+        <v>0.25</v>
       </c>
       <c r="AE22" t="b">
         <v>1</v>
       </c>
       <c r="AF22" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>226.38</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>205.68</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>10.8</v>
-      </c>
+        <v>19.61</v>
+      </c>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="n">
-        <v>232.7375571148825</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="AK22" t="n">
-        <v>-8.5</v>
+        <v>31.6</v>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
@@ -5607,62 +5607,62 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="AQ22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AS22" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AW22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AX22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>8585000</v>
       </c>
       <c r="BA22" t="n">
-        <v>5704863</v>
+        <v>8585000</v>
       </c>
       <c r="BB22" t="n">
-        <v>5704863</v>
+        <v>8585000</v>
       </c>
       <c r="BC22" t="n">
-        <v>5704863</v>
+        <v>8585000</v>
       </c>
       <c r="BD22" t="n">
         <v>0</v>
@@ -5698,7 +5698,7 @@
         <v>0</v>
       </c>
       <c r="BO22" t="n">
-        <v>5704863</v>
+        <v>8585000</v>
       </c>
       <c r="BP22" t="n">
         <v>1</v>
@@ -5785,13 +5785,13 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>1.09</v>
+        <v>1.078</v>
       </c>
       <c r="W23" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="X23" t="n">
-        <v>5.32</v>
+        <v>5.38</v>
       </c>
       <c r="Y23" t="n">
         <v>31</v>
@@ -6013,13 +6013,13 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>0.391</v>
+        <v>0.403</v>
       </c>
       <c r="W24" t="n">
-        <v>1006</v>
+        <v>977</v>
       </c>
       <c r="X24" t="n">
-        <v>51.3</v>
+        <v>49.8</v>
       </c>
       <c r="Y24" t="n">
         <v>21</v>
@@ -6245,10 +6245,10 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>0.262</v>
+        <v>0.261</v>
       </c>
       <c r="W25" t="n">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="X25" t="n">
         <v>27.1</v>
@@ -6477,13 +6477,13 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>0.13</v>
+        <v>0.127</v>
       </c>
       <c r="W26" t="n">
-        <v>615</v>
+        <v>632</v>
       </c>
       <c r="X26" t="n">
-        <v>13.5</v>
+        <v>13.9</v>
       </c>
       <c r="Y26" t="n">
         <v>-1</v>
@@ -6709,13 +6709,13 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>0.523</v>
+        <v>0.517</v>
       </c>
       <c r="W27" t="n">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="X27" t="n">
-        <v>35.4</v>
+        <v>35.8</v>
       </c>
       <c r="Y27" t="n">
         <v>21</v>
@@ -6941,10 +6941,10 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>1.893</v>
+        <v>1.876</v>
       </c>
       <c r="W28" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="n">
@@ -7171,13 +7171,13 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>0.042</v>
+        <v>0.041</v>
       </c>
       <c r="W29" t="n">
-        <v>1631</v>
+        <v>1672</v>
       </c>
       <c r="X29" t="n">
-        <v>21.3</v>
+        <v>21.9</v>
       </c>
       <c r="Y29" t="n">
         <v>10</v>
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>0.532</v>
+        <v>0.504</v>
       </c>
       <c r="W30" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="X30" t="n">
-        <v>35.1</v>
+        <v>36.9</v>
       </c>
       <c r="Y30" t="n">
         <v>-44</v>
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>0.26</v>
+        <v>0.255</v>
       </c>
       <c r="W31" t="n">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="X31" t="n">
-        <v>13.2</v>
+        <v>13.4</v>
       </c>
       <c r="Y31" t="n">
         <v>16</v>
@@ -8093,13 +8093,13 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>0.232</v>
+        <v>0.236</v>
       </c>
       <c r="W33" t="n">
-        <v>1718</v>
+        <v>1690</v>
       </c>
       <c r="X33" t="n">
-        <v>18.2</v>
+        <v>17.9</v>
       </c>
       <c r="Y33" t="n">
         <v>-3</v>
@@ -8328,7 +8328,7 @@
         <v>0.043</v>
       </c>
       <c r="W34" t="n">
-        <v>3159</v>
+        <v>3149</v>
       </c>
       <c r="X34" t="n">
         <v>18.7</v>
@@ -8557,13 +8557,13 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>0.371</v>
+        <v>0.37</v>
       </c>
       <c r="W35" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="X35" t="n">
-        <v>93.2</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="Y35" t="n">
         <v>246</v>
@@ -8789,13 +8789,13 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>0.677</v>
+        <v>0.64</v>
       </c>
       <c r="W36" t="n">
-        <v>347</v>
+        <v>367</v>
       </c>
       <c r="X36" t="n">
-        <v>1120</v>
+        <v>1183</v>
       </c>
       <c r="Y36" t="n">
         <v>-61</v>
@@ -9017,13 +9017,13 @@
         </is>
       </c>
       <c r="V37" t="n">
-        <v>0.863</v>
+        <v>0.835</v>
       </c>
       <c r="W37" t="n">
-        <v>3663</v>
+        <v>3786</v>
       </c>
       <c r="X37" t="n">
-        <v>25.6</v>
+        <v>26.5</v>
       </c>
       <c r="Y37" t="n">
         <v>2</v>
@@ -9252,10 +9252,10 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>5244</v>
+        <v>5337</v>
       </c>
       <c r="X38" t="n">
-        <v>12.3</v>
+        <v>12.5</v>
       </c>
       <c r="Y38" t="n">
         <v>26</v>
@@ -9481,13 +9481,13 @@
         </is>
       </c>
       <c r="V39" t="n">
-        <v>0.105</v>
+        <v>0.101</v>
       </c>
       <c r="W39" t="n">
-        <v>471</v>
+        <v>490</v>
       </c>
       <c r="X39" t="n">
-        <v>7.61</v>
+        <v>7.92</v>
       </c>
       <c r="Y39" t="n">
         <v>118</v>
@@ -9712,7 +9712,7 @@
         <v>0.011</v>
       </c>
       <c r="W40" t="n">
-        <v>4123</v>
+        <v>4134</v>
       </c>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="n">
@@ -9867,12 +9867,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CHEMBOND</t>
+          <t>HINDCON</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
+          <t>Hindcon Chemicals Limited</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -9884,40 +9884,40 @@
         </is>
       </c>
       <c r="E41" t="n">
+        <v>7</v>
+      </c>
+      <c r="F41" t="n">
         <v>4</v>
-      </c>
-      <c r="F41" t="n">
-        <v>8</v>
       </c>
       <c r="G41" t="n">
         <v>25</v>
       </c>
       <c r="H41" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>189.25</v>
+        <v>28.46</v>
       </c>
       <c r="J41" t="n">
-        <v>170.45</v>
+        <v>23.55</v>
       </c>
       <c r="K41" t="n">
-        <v>11</v>
+        <v>20.8</v>
       </c>
       <c r="L41" t="n">
-        <v>67.54000000000001</v>
+        <v>68.34</v>
       </c>
       <c r="M41" t="n">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="N41" t="n">
-        <v>2560187</v>
+        <v>2018403</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2560187</v>
+        <v>2018403</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -9931,94 +9931,94 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
       <c r="V41" t="n">
-        <v>0.1</v>
+        <v>0.146</v>
       </c>
       <c r="W41" t="n">
-        <v>255</v>
+        <v>138</v>
       </c>
       <c r="X41" t="n">
-        <v>27.2</v>
+        <v>32</v>
       </c>
       <c r="Y41" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.87</v>
+        <v>3.17</v>
       </c>
       <c r="AA41" t="n">
-        <v>-31</v>
+        <v>7</v>
       </c>
       <c r="AB41" t="n">
-        <v>3.36</v>
+        <v>0.49</v>
       </c>
       <c r="AC41" t="n">
-        <v>4.96</v>
+        <v>8.76</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AE41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.97</v>
+        <v>14.87</v>
       </c>
       <c r="AG41" t="n">
-        <v>182.38</v>
+        <v>24.83</v>
       </c>
       <c r="AH41" t="n">
-        <v>164.81</v>
+        <v>22.86</v>
       </c>
       <c r="AI41" t="n">
-        <v>31.2</v>
+        <v>22.8</v>
       </c>
       <c r="AJ41" t="n">
-        <v>170.4518641810919</v>
+        <v>23.5472893358377</v>
       </c>
       <c r="AK41" t="n">
-        <v>11</v>
+        <v>20.9</v>
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>Aging</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AR41" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="AS41" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="AT41" t="n">
         <v>0</v>
@@ -10027,13 +10027,13 @@
         <v>0</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AW41" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="AX41" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="AY41" t="n">
         <v>0</v>
@@ -10042,13 +10042,13 @@
         <v>0</v>
       </c>
       <c r="BA41" t="n">
-        <v>0</v>
+        <v>1308280</v>
       </c>
       <c r="BB41" t="n">
-        <v>2560187</v>
+        <v>2018403</v>
       </c>
       <c r="BC41" t="n">
-        <v>2560187</v>
+        <v>2018403</v>
       </c>
       <c r="BD41" t="n">
         <v>0</v>
@@ -10084,10 +10084,10 @@
         <v>0</v>
       </c>
       <c r="BO41" t="n">
-        <v>0</v>
+        <v>1308280</v>
       </c>
       <c r="BP41" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BQ41" t="n">
         <v>0</v>
@@ -10099,16 +10099,16 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>HINDCON</t>
+          <t>ASAHISONG</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Hindcon Chemicals Limited</t>
+          <t>ASAHI SONGWON COLORS LIMITED</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -10116,40 +10116,40 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="G42" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>28.46</v>
+        <v>365.05</v>
       </c>
       <c r="J42" t="n">
-        <v>23.55</v>
+        <v>338.1</v>
       </c>
       <c r="K42" t="n">
-        <v>20.8</v>
+        <v>8</v>
       </c>
       <c r="L42" t="n">
-        <v>68.34</v>
+        <v>66.73</v>
       </c>
       <c r="M42" t="n">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="N42" t="n">
-        <v>2018403</v>
+        <v>3381000</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2018403</v>
+        <v>3381000</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -10163,69 +10163,69 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="V42" t="n">
-        <v>0.138</v>
+        <v>0.076</v>
       </c>
       <c r="W42" t="n">
-        <v>146</v>
+        <v>444</v>
       </c>
       <c r="X42" t="n">
-        <v>33.6</v>
+        <v>13.1</v>
       </c>
       <c r="Y42" t="n">
-        <v>19</v>
+        <v>-8</v>
       </c>
       <c r="Z42" t="n">
-        <v>3.17</v>
+        <v>24</v>
       </c>
       <c r="AA42" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.49</v>
+        <v>14.36</v>
       </c>
       <c r="AC42" t="n">
-        <v>8.76</v>
+        <v>9.94</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="AE42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF42" t="n">
-        <v>14.87</v>
+        <v>18</v>
       </c>
       <c r="AG42" t="n">
-        <v>24.83</v>
+        <v>370.99</v>
       </c>
       <c r="AH42" t="n">
-        <v>22.86</v>
+        <v>275.33</v>
       </c>
       <c r="AI42" t="n">
-        <v>22.8</v>
+        <v>60.2</v>
       </c>
       <c r="AJ42" t="n">
-        <v>23.5472893358377</v>
+        <v>338.1</v>
       </c>
       <c r="AK42" t="n">
-        <v>20.9</v>
+        <v>8</v>
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Stale</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Stale Accumulation</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
@@ -10235,22 +10235,22 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="AQ42" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AR42" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="AS42" t="n">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="AT42" t="n">
         <v>0</v>
@@ -10259,13 +10259,13 @@
         <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AX42" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="AY42" t="n">
         <v>0</v>
@@ -10274,13 +10274,13 @@
         <v>0</v>
       </c>
       <c r="BA42" t="n">
-        <v>1308280</v>
+        <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>2018403</v>
+        <v>0</v>
       </c>
       <c r="BC42" t="n">
-        <v>2018403</v>
+        <v>3381000</v>
       </c>
       <c r="BD42" t="n">
         <v>0</v>
@@ -10316,10 +10316,10 @@
         <v>0</v>
       </c>
       <c r="BO42" t="n">
-        <v>1308280</v>
+        <v>0</v>
       </c>
       <c r="BP42" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="BQ42" t="n">
         <v>0</v>
@@ -10331,57 +10331,57 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ASAHISONG</t>
+          <t>CHEMBOND</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ASAHI SONGWON COLORS LIMITED</t>
+          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C43" t="n">
+        <v>24</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" t="n">
+        <v>8</v>
+      </c>
+      <c r="G43" t="n">
         <v>25</v>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" t="n">
-        <v>15</v>
-      </c>
-      <c r="G43" t="n">
-        <v>17</v>
-      </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I43" t="n">
-        <v>365.05</v>
+        <v>189.25</v>
       </c>
       <c r="J43" t="n">
-        <v>338.1</v>
+        <v>170.45</v>
       </c>
       <c r="K43" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L43" t="n">
-        <v>66.73</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="M43" t="n">
-        <v>0.34</v>
+        <v>0.26</v>
       </c>
       <c r="N43" t="n">
-        <v>3381000</v>
+        <v>2560187</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>3381000</v>
+        <v>2560187</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -10395,94 +10395,94 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="V43" t="n">
-        <v>0.079</v>
+        <v>0.097</v>
       </c>
       <c r="W43" t="n">
-        <v>430</v>
+        <v>265</v>
       </c>
       <c r="X43" t="n">
-        <v>12.7</v>
+        <v>28.4</v>
       </c>
       <c r="Y43" t="n">
-        <v>-8</v>
+        <v>24</v>
       </c>
       <c r="Z43" t="n">
-        <v>24</v>
+        <v>1.87</v>
       </c>
       <c r="AA43" t="n">
-        <v>33</v>
+        <v>-31</v>
       </c>
       <c r="AB43" t="n">
-        <v>14.36</v>
+        <v>3.36</v>
       </c>
       <c r="AC43" t="n">
-        <v>9.94</v>
+        <v>4.96</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>1</v>
       </c>
       <c r="AF43" t="n">
-        <v>18</v>
+        <v>2.97</v>
       </c>
       <c r="AG43" t="n">
-        <v>370.99</v>
+        <v>182.38</v>
       </c>
       <c r="AH43" t="n">
-        <v>275.33</v>
+        <v>164.81</v>
       </c>
       <c r="AI43" t="n">
-        <v>60.2</v>
+        <v>31.2</v>
       </c>
       <c r="AJ43" t="n">
-        <v>338.1</v>
+        <v>170.4518641810919</v>
       </c>
       <c r="AK43" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Stale Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="AQ43" t="n">
         <v>0</v>
       </c>
       <c r="AR43" t="n">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="AS43" t="n">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="AT43" t="n">
         <v>0</v>
@@ -10494,10 +10494,10 @@
         <v>0</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY43" t="n">
         <v>0</v>
@@ -10509,10 +10509,10 @@
         <v>0</v>
       </c>
       <c r="BB43" t="n">
-        <v>0</v>
+        <v>2560187</v>
       </c>
       <c r="BC43" t="n">
-        <v>3381000</v>
+        <v>2560187</v>
       </c>
       <c r="BD43" t="n">
         <v>0</v>
@@ -10551,7 +10551,7 @@
         <v>0</v>
       </c>
       <c r="BP43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ43" t="n">
         <v>0</v>
@@ -10635,10 +10635,10 @@
         </is>
       </c>
       <c r="V44" t="n">
-        <v>0.051</v>
+        <v>0.052</v>
       </c>
       <c r="W44" t="n">
-        <v>958</v>
+        <v>945</v>
       </c>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="n">
@@ -10868,10 +10868,10 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>3656</v>
+        <v>3740</v>
       </c>
       <c r="X45" t="n">
-        <v>82.3</v>
+        <v>84.2</v>
       </c>
       <c r="Y45" t="n">
         <v>42</v>
@@ -11100,7 +11100,7 @@
         <v>0.006</v>
       </c>
       <c r="W46" t="n">
-        <v>4839</v>
+        <v>4860</v>
       </c>
       <c r="X46" t="n">
         <v>12.5</v>
@@ -11328,10 +11328,10 @@
         <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>103712</v>
+        <v>102815</v>
       </c>
       <c r="X47" t="n">
-        <v>29.9</v>
+        <v>29.6</v>
       </c>
       <c r="Y47" t="n">
         <v>18</v>
@@ -11557,13 +11557,13 @@
         </is>
       </c>
       <c r="V48" t="n">
-        <v>0.234</v>
+        <v>0.236</v>
       </c>
       <c r="W48" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="X48" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="Y48" t="n">
         <v>21</v>
@@ -12454,70 +12454,70 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HTEL</t>
+          <t>JAYAGROGN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers Limited</t>
+          <t>Jayant Agro-Organics Limited</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>90.37</v>
+        <v>212.86</v>
       </c>
       <c r="D21" t="n">
-        <v>68.68000000000001</v>
+        <v>232.74</v>
       </c>
       <c r="E21" t="n">
-        <v>31.6</v>
+        <v>-8.5</v>
       </c>
       <c r="F21" t="n">
-        <v>71.22</v>
+        <v>67.13</v>
       </c>
       <c r="G21" t="n">
-        <v>0.86</v>
+        <v>0.57</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JAYAGROGN</t>
+          <t>HTEL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jayant Agro-Organics Limited</t>
+          <t>Hy-Tech Engineers Limited</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>212.86</v>
+        <v>90.37</v>
       </c>
       <c r="D22" t="n">
-        <v>232.74</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>-8.5</v>
+        <v>31.6</v>
       </c>
       <c r="F22" t="n">
-        <v>67.13</v>
+        <v>71.22</v>
       </c>
       <c r="G22" t="n">
-        <v>0.57</v>
+        <v>0.86</v>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
     </row>
@@ -13154,105 +13154,105 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CHEMBOND</t>
+          <t>HINDCON</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
+          <t>Hindcon Chemicals Limited</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>189.25</v>
+        <v>28.46</v>
       </c>
       <c r="D41" t="n">
-        <v>170.45</v>
+        <v>23.55</v>
       </c>
       <c r="E41" t="n">
-        <v>11</v>
+        <v>20.8</v>
       </c>
       <c r="F41" t="n">
-        <v>67.54000000000001</v>
+        <v>68.34</v>
       </c>
       <c r="G41" t="n">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="H41" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>HINDCON</t>
+          <t>ASAHISONG</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Hindcon Chemicals Limited</t>
+          <t>ASAHI SONGWON COLORS LIMITED</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>28.46</v>
+        <v>365.05</v>
       </c>
       <c r="D42" t="n">
-        <v>23.55</v>
+        <v>338.1</v>
       </c>
       <c r="E42" t="n">
-        <v>20.8</v>
+        <v>8</v>
       </c>
       <c r="F42" t="n">
-        <v>68.34</v>
+        <v>66.73</v>
       </c>
       <c r="G42" t="n">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="H42" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ASAHISONG</t>
+          <t>CHEMBOND</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ASAHI SONGWON COLORS LIMITED</t>
+          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>365.05</v>
+        <v>189.25</v>
       </c>
       <c r="D43" t="n">
-        <v>338.1</v>
+        <v>170.45</v>
       </c>
       <c r="E43" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F43" t="n">
-        <v>66.73</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="G43" t="n">
-        <v>0.34</v>
+        <v>0.26</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
     </row>

--- a/output/2026-10-12/enriched_analysis.xlsx
+++ b/output/2026-10-12/enriched_analysis.xlsx
@@ -886,13 +886,13 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>83.67</v>
+        <v>84.18000000000001</v>
       </c>
       <c r="J2" t="n">
         <v>77.33</v>
       </c>
       <c r="K2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="L2" t="n">
         <v>61.32</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>2.253</v>
+        <v>2.251</v>
       </c>
       <c r="W2" t="n">
-        <v>2796</v>
+        <v>2799</v>
       </c>
       <c r="X2" t="n">
         <v>21.9</v>
@@ -962,19 +962,19 @@
         <v>6</v>
       </c>
       <c r="AG2" t="n">
-        <v>82.23999999999999</v>
+        <v>82.36</v>
       </c>
       <c r="AH2" t="n">
-        <v>58.74</v>
+        <v>58.99</v>
       </c>
       <c r="AI2" t="n">
-        <v>55.4</v>
+        <v>53.5</v>
       </c>
       <c r="AJ2" t="n">
         <v>77.33020135925074</v>
       </c>
       <c r="AK2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1118,13 +1118,13 @@
         <v>-1</v>
       </c>
       <c r="I3" t="n">
-        <v>795.9</v>
+        <v>811</v>
       </c>
       <c r="J3" t="n">
         <v>819.08</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.8</v>
+        <v>-1</v>
       </c>
       <c r="L3" t="n">
         <v>73</v>
@@ -1161,13 +1161,13 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>0.878</v>
+        <v>0.869</v>
       </c>
       <c r="W3" t="n">
-        <v>922</v>
+        <v>932</v>
       </c>
       <c r="X3" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Y3" t="n">
         <v>47</v>
@@ -1194,19 +1194,19 @@
         <v>25.79</v>
       </c>
       <c r="AG3" t="n">
-        <v>789.1900000000001</v>
+        <v>790.71</v>
       </c>
       <c r="AH3" t="n">
-        <v>670.52</v>
+        <v>671.01</v>
       </c>
       <c r="AI3" t="n">
-        <v>39.4</v>
+        <v>37.8</v>
       </c>
       <c r="AJ3" t="n">
         <v>819.0814633455414</v>
       </c>
       <c r="AK3" t="n">
-        <v>-2.8</v>
+        <v>-1</v>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
@@ -1350,13 +1350,13 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>296.55</v>
+        <v>308</v>
       </c>
       <c r="J4" t="n">
         <v>265.56</v>
       </c>
       <c r="K4" t="n">
-        <v>11.7</v>
+        <v>16</v>
       </c>
       <c r="L4" t="n">
         <v>64.63</v>
@@ -1396,7 +1396,7 @@
         <v>0.044</v>
       </c>
       <c r="W4" t="n">
-        <v>3016</v>
+        <v>3018</v>
       </c>
       <c r="X4" t="n">
         <v>10.4</v>
@@ -1426,19 +1426,19 @@
         <v>16</v>
       </c>
       <c r="AG4" t="n">
-        <v>259.42</v>
+        <v>261.24</v>
       </c>
       <c r="AH4" t="n">
-        <v>183.24</v>
+        <v>184.06</v>
       </c>
       <c r="AI4" t="n">
-        <v>120.4</v>
+        <v>128.5</v>
       </c>
       <c r="AJ4" t="n">
         <v>265.56012</v>
       </c>
       <c r="AK4" t="n">
-        <v>11.7</v>
+        <v>16</v>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
@@ -1553,57 +1553,57 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PKTEA</t>
+          <t>BMWVENTLTD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
+          <t>BMW VENTURES LIMITED</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Watchlist</t>
+          <t>Fundamental Watch</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="G5" t="n">
         <v>21</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I5" t="n">
-        <v>899</v>
+        <v>63.25</v>
       </c>
       <c r="J5" t="n">
-        <v>869.9299999999999</v>
+        <v>55.06</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3</v>
+        <v>14.9</v>
       </c>
       <c r="L5" t="n">
-        <v>61.71</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>5.19</v>
+        <v>2.9</v>
       </c>
       <c r="N5" t="n">
-        <v>51906767</v>
+        <v>28991535</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>51906767</v>
+        <v>28991535</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1617,58 +1617,60 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>1.93</v>
+        <v>0.533</v>
       </c>
       <c r="W5" t="n">
-        <v>269</v>
-      </c>
-      <c r="X5" t="inlineStr"/>
+        <v>544</v>
+      </c>
+      <c r="X5" t="n">
+        <v>13.6</v>
+      </c>
       <c r="Y5" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.91</v>
+        <v>21</v>
       </c>
       <c r="AA5" t="n">
-        <v>-184</v>
+        <v>20</v>
       </c>
       <c r="AB5" t="n">
-        <v>31.98</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.26</v>
+        <v>12</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.1</v>
+        <v>0.58</v>
       </c>
       <c r="AE5" t="b">
         <v>1</v>
       </c>
       <c r="AF5" t="n">
-        <v>57.93</v>
+        <v>3.4</v>
       </c>
       <c r="AG5" t="n">
-        <v>846.5700000000001</v>
+        <v>55.11</v>
       </c>
       <c r="AH5" t="n">
-        <v>793.78</v>
+        <v>57.65</v>
       </c>
       <c r="AI5" t="n">
         <v>10.1</v>
       </c>
       <c r="AJ5" t="n">
-        <v>869.9263759469062</v>
+        <v>55.06464387464388</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.3</v>
+        <v>14.9</v>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
@@ -1682,57 +1684,57 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AR5" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="AS5" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AX5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>21263036</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>30615178</v>
+        <v>10009832</v>
       </c>
       <c r="BB5" t="n">
-        <v>51906767</v>
+        <v>19968394</v>
       </c>
       <c r="BC5" t="n">
-        <v>51906767</v>
+        <v>28991535</v>
       </c>
       <c r="BD5" t="n">
         <v>0</v>
@@ -1768,7 +1770,7 @@
         <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>30615178</v>
+        <v>10009832</v>
       </c>
       <c r="BP5" t="n">
         <v>1</v>
@@ -1783,12 +1785,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SIGIND</t>
+          <t>SRHHYPOLTD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Signet Industries Limited</t>
+          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1800,40 +1802,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G6" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>61.05</v>
+        <v>541.3</v>
       </c>
       <c r="J6" t="n">
-        <v>74.22</v>
+        <v>510.94</v>
       </c>
       <c r="K6" t="n">
-        <v>-17.7</v>
+        <v>5.9</v>
       </c>
       <c r="L6" t="n">
-        <v>72.56999999999999</v>
+        <v>61.84</v>
       </c>
       <c r="M6" t="n">
-        <v>2.01</v>
+        <v>3.06</v>
       </c>
       <c r="N6" t="n">
-        <v>20066329</v>
+        <v>30622049</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>20066329</v>
+        <v>30622049</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1847,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1855,52 +1857,52 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>1.173</v>
+        <v>0.329</v>
       </c>
       <c r="W6" t="n">
-        <v>171</v>
+        <v>930</v>
       </c>
       <c r="X6" t="n">
-        <v>7.24</v>
+        <v>9.15</v>
       </c>
       <c r="Y6" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="Z6" t="n">
-        <v>27.97</v>
+        <v>30</v>
       </c>
       <c r="AA6" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.73</v>
+        <v>14.66</v>
       </c>
       <c r="AC6" t="n">
-        <v>13.6</v>
+        <v>14.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.86</v>
+        <v>0.01</v>
       </c>
       <c r="AE6" t="b">
         <v>1</v>
       </c>
       <c r="AF6" t="n">
-        <v>9.140000000000001</v>
+        <v>14</v>
       </c>
       <c r="AG6" t="n">
-        <v>67.55</v>
+        <v>519.48</v>
       </c>
       <c r="AH6" t="n">
-        <v>53.42</v>
+        <v>492.51</v>
       </c>
       <c r="AI6" t="n">
-        <v>25.6</v>
+        <v>22.1</v>
       </c>
       <c r="AJ6" t="n">
-        <v>74.21830535305453</v>
+        <v>510.9380308010612</v>
       </c>
       <c r="AK6" t="n">
-        <v>-17.7</v>
+        <v>5.9</v>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
@@ -1919,7 +1921,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -1928,10 +1930,10 @@
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="AR6" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="AS6" t="n">
         <v>21</v>
@@ -1943,67 +1945,67 @@
         <v>0</v>
       </c>
       <c r="AV6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>13311661</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>30622049</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>30622049</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>13311661</v>
+      </c>
+      <c r="BP6" t="n">
         <v>2</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>1525105</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>20066329</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>20066329</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>1525105</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>1</v>
       </c>
       <c r="BQ6" t="n">
         <v>0</v>
@@ -2015,16 +2017,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NURECA</t>
+          <t>SIGIND</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NURECA LIMITED</t>
+          <t>Signet Industries Limited</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2032,40 +2034,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G7" t="n">
         <v>13</v>
       </c>
       <c r="H7" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>331.65</v>
+        <v>58.05</v>
       </c>
       <c r="J7" t="n">
-        <v>333.11</v>
+        <v>74.22</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.4</v>
+        <v>-21.8</v>
       </c>
       <c r="L7" t="n">
-        <v>63.24</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>3.75</v>
+        <v>2.01</v>
       </c>
       <c r="N7" t="n">
-        <v>37538354</v>
+        <v>20066329</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>37538354</v>
+        <v>20066329</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -2079,60 +2081,60 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>1.199</v>
+        <v>1.167</v>
       </c>
       <c r="W7" t="n">
-        <v>313</v>
+        <v>172</v>
       </c>
       <c r="X7" t="n">
-        <v>144</v>
+        <v>7.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.45</v>
+        <v>27.97</v>
       </c>
       <c r="AA7" t="n">
-        <v>264</v>
+        <v>17</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.55</v>
+        <v>2.73</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.07</v>
+        <v>13.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.01</v>
+        <v>1.86</v>
       </c>
       <c r="AE7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF7" t="n">
-        <v>6.06</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AG7" t="n">
-        <v>333.49</v>
+        <v>67.72</v>
       </c>
       <c r="AH7" t="n">
-        <v>284.39</v>
+        <v>53.44</v>
       </c>
       <c r="AI7" t="n">
-        <v>29.9</v>
+        <v>20.3</v>
       </c>
       <c r="AJ7" t="n">
-        <v>333.1146252074293</v>
+        <v>74.21830535305453</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0.4</v>
+        <v>-21.8</v>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
@@ -2151,52 +2153,52 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>24-07-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="AR7" t="n">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="AS7" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="AW7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX7" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="AY7" t="n">
         <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>7328762</v>
+        <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>19454866</v>
+        <v>1525105</v>
       </c>
       <c r="BB7" t="n">
-        <v>23414636</v>
+        <v>20066329</v>
       </c>
       <c r="BC7" t="n">
-        <v>37538354</v>
+        <v>20066329</v>
       </c>
       <c r="BD7" t="n">
         <v>0</v>
@@ -2232,10 +2234,10 @@
         <v>0</v>
       </c>
       <c r="BO7" t="n">
-        <v>19454866</v>
+        <v>1525105</v>
       </c>
       <c r="BP7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BQ7" t="n">
         <v>0</v>
@@ -2247,16 +2249,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>PKTEA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>THANGAMAYIL JEWELLERY LIMITED</t>
+          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2264,40 +2266,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="F8" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>4889.5</v>
+        <v>865.3</v>
       </c>
       <c r="J8" t="n">
-        <v>5198.76</v>
+        <v>869.9299999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.9</v>
+        <v>-0.5</v>
       </c>
       <c r="L8" t="n">
-        <v>67.16</v>
+        <v>61.71</v>
       </c>
       <c r="M8" t="n">
-        <v>7.21</v>
+        <v>5.19</v>
       </c>
       <c r="N8" t="n">
-        <v>72054758</v>
+        <v>51906767</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>72054758</v>
+        <v>51906767</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2311,124 +2313,122 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>0.047</v>
+        <v>1.937</v>
       </c>
       <c r="W8" t="n">
-        <v>15182</v>
-      </c>
-      <c r="X8" t="n">
-        <v>38.6</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="X8" t="inlineStr"/>
       <c r="Y8" t="n">
-        <v>83</v>
+        <v>9</v>
       </c>
       <c r="Z8" t="n">
-        <v>145</v>
+        <v>11.91</v>
       </c>
       <c r="AA8" t="n">
-        <v>264</v>
+        <v>-184</v>
       </c>
       <c r="AB8" t="n">
-        <v>27.38</v>
+        <v>31.98</v>
       </c>
       <c r="AC8" t="n">
-        <v>25.5</v>
+        <v>-0.26</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.64</v>
+        <v>0.1</v>
       </c>
       <c r="AE8" t="b">
         <v>1</v>
       </c>
       <c r="AF8" t="n">
+        <v>57.93</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>850.0700000000001</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>794.41</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>869.9263759469062</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>17-08-2026</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>30-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>56</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV8" t="n">
         <v>5</v>
       </c>
-      <c r="AG8" t="n">
-        <v>5189.82</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>4532.93</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>5198.755988455989</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>-5.9</v>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>Aging</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Mature Accumulation</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>Mature — Wait for Pullback</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>04-08-2026</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>31-08-2026</t>
-        </is>
-      </c>
-      <c r="AQ8" t="n">
-        <v>27</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>69</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
       <c r="AW8" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AX8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AY8" t="n">
         <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>21263036</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>30615178</v>
       </c>
       <c r="BB8" t="n">
-        <v>19879002</v>
+        <v>51906767</v>
       </c>
       <c r="BC8" t="n">
-        <v>72054758</v>
+        <v>51906767</v>
       </c>
       <c r="BD8" t="n">
         <v>0</v>
@@ -2464,10 +2464,10 @@
         <v>0</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>30615178</v>
       </c>
       <c r="BP8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BQ8" t="n">
         <v>0</v>
@@ -2479,16 +2479,16 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BMWVENTLTD</t>
+          <t>NURECA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BMW VENTURES LIMITED</t>
+          <t>NURECA LIMITED</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2496,40 +2496,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F9" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H9" t="n">
         <v>-1</v>
       </c>
       <c r="I9" t="n">
-        <v>57.95</v>
+        <v>331.4</v>
       </c>
       <c r="J9" t="n">
-        <v>55.06</v>
+        <v>333.11</v>
       </c>
       <c r="K9" t="n">
-        <v>5.2</v>
+        <v>-0.5</v>
       </c>
       <c r="L9" t="n">
-        <v>73.01000000000001</v>
+        <v>63.24</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>3.75</v>
       </c>
       <c r="N9" t="n">
-        <v>28991535</v>
+        <v>37538354</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>28991535</v>
+        <v>37538354</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2543,163 +2543,163 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>22-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>0.528</v>
+        <v>1.192</v>
       </c>
       <c r="W9" t="n">
-        <v>549</v>
+        <v>315</v>
       </c>
       <c r="X9" t="n">
-        <v>13.8</v>
+        <v>145</v>
       </c>
       <c r="Y9" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>264</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>333.68</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>284.64</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>333.1146252074293</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>24-07-2026</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>30-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>68</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>80</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW9" t="n">
         <v>19</v>
       </c>
-      <c r="Z9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>54.97</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>57.62</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>55.06464387464388</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>05-08-2026</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>22-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ9" t="n">
-        <v>48</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>68</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
+      <c r="AX9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>7328762</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>19454866</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>23414636</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>37538354</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>19454866</v>
+      </c>
+      <c r="BP9" t="n">
         <v>3</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>10009832</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>19968394</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>28991535</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>10009832</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>1</v>
       </c>
       <c r="BQ9" t="n">
         <v>0</v>
@@ -2711,16 +2711,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DIAMONDYD</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Prataap Snacks Limited</t>
+          <t>THANGAMAYIL JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2728,40 +2728,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G10" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H10" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1049.4</v>
+        <v>4890.5</v>
       </c>
       <c r="J10" t="n">
-        <v>1175.33</v>
+        <v>5198.76</v>
       </c>
       <c r="K10" t="n">
-        <v>-10.7</v>
+        <v>-5.9</v>
       </c>
       <c r="L10" t="n">
-        <v>64.3</v>
+        <v>67.16</v>
       </c>
       <c r="M10" t="n">
-        <v>58.7</v>
+        <v>7.21</v>
       </c>
       <c r="N10" t="n">
-        <v>586966134</v>
+        <v>72054758</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>586966134</v>
+        <v>72054758</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2775,163 +2775,163 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>2.362</v>
+        <v>0.047</v>
       </c>
       <c r="W10" t="n">
-        <v>2485</v>
+        <v>15191</v>
       </c>
       <c r="X10" t="n">
-        <v>195</v>
+        <v>38.7</v>
       </c>
       <c r="Y10" t="n">
-        <v>6</v>
+        <v>83</v>
       </c>
       <c r="Z10" t="n">
-        <v>19.05</v>
+        <v>145</v>
       </c>
       <c r="AA10" t="n">
-        <v>194</v>
+        <v>264</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.03</v>
+        <v>27.38</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.17</v>
+        <v>25.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.06</v>
+        <v>0.64</v>
       </c>
       <c r="AE10" t="b">
         <v>1</v>
       </c>
       <c r="AF10" t="n">
-        <v>3.87</v>
+        <v>5</v>
       </c>
       <c r="AG10" t="n">
-        <v>1135</v>
+        <v>5171.49</v>
       </c>
       <c r="AH10" t="n">
-        <v>1089.64</v>
+        <v>4540.81</v>
       </c>
       <c r="AI10" t="n">
-        <v>5.4</v>
+        <v>19.7</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1175.326204878987</v>
+        <v>5198.755988455989</v>
       </c>
       <c r="AK10" t="n">
-        <v>-10.7</v>
+        <v>-5.9</v>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Stale Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>04-08-2026</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="AQ10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>69</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
         <v>2</v>
       </c>
-      <c r="AR10" t="n">
-        <v>68</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>66</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
       <c r="AX10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>19879002</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>72054758</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP10" t="n">
         <v>3</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>586966134</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>1</v>
       </c>
       <c r="BQ10" t="n">
         <v>0</v>
@@ -2943,16 +2943,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SRHHYPOLTD</t>
+          <t>DIAMONDYD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
+          <t>Prataap Snacks Limited</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2960,40 +2960,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F11" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G11" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I11" t="n">
-        <v>533.85</v>
+        <v>1045.4</v>
       </c>
       <c r="J11" t="n">
-        <v>510.94</v>
+        <v>1175.33</v>
       </c>
       <c r="K11" t="n">
-        <v>4.5</v>
+        <v>-11.1</v>
       </c>
       <c r="L11" t="n">
-        <v>61.84</v>
+        <v>64.3</v>
       </c>
       <c r="M11" t="n">
-        <v>3.06</v>
+        <v>58.7</v>
       </c>
       <c r="N11" t="n">
-        <v>30622049</v>
+        <v>586966134</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>30622049</v>
+        <v>586966134</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -3007,94 +3007,94 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>0.334</v>
+        <v>2.341</v>
       </c>
       <c r="W11" t="n">
-        <v>916</v>
+        <v>2507</v>
       </c>
       <c r="X11" t="n">
-        <v>8.98</v>
+        <v>197</v>
       </c>
       <c r="Y11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z11" t="n">
-        <v>30</v>
+        <v>19.05</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="AB11" t="n">
-        <v>14.66</v>
+        <v>1.03</v>
       </c>
       <c r="AC11" t="n">
-        <v>14.4</v>
+        <v>3.17</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="AE11" t="b">
         <v>1</v>
       </c>
       <c r="AF11" t="n">
-        <v>14</v>
+        <v>3.87</v>
       </c>
       <c r="AG11" t="n">
-        <v>518.38</v>
+        <v>1133.4</v>
       </c>
       <c r="AH11" t="n">
-        <v>492.39</v>
+        <v>1089.4</v>
       </c>
       <c r="AI11" t="n">
-        <v>18.8</v>
+        <v>3.7</v>
       </c>
       <c r="AJ11" t="n">
-        <v>510.9380308010612</v>
+        <v>1175.326204878987</v>
       </c>
       <c r="AK11" t="n">
-        <v>4.5</v>
+        <v>-11.1</v>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Stale</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Stale Accumulation</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="AR11" t="n">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="AS11" t="n">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="AT11" t="n">
         <v>0</v>
@@ -3103,13 +3103,13 @@
         <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="AY11" t="n">
         <v>0</v>
@@ -3118,13 +3118,13 @@
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>13311661</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>30622049</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>30622049</v>
+        <v>586966134</v>
       </c>
       <c r="BD11" t="n">
         <v>0</v>
@@ -3160,10 +3160,10 @@
         <v>0</v>
       </c>
       <c r="BO11" t="n">
-        <v>13311661</v>
+        <v>0</v>
       </c>
       <c r="BP11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ11" t="n">
         <v>0</v>
@@ -3204,13 +3204,13 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>364.9</v>
+        <v>380.35</v>
       </c>
       <c r="J12" t="n">
         <v>217.8</v>
       </c>
       <c r="K12" t="n">
-        <v>67.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="L12" t="n">
         <v>71.75</v>
@@ -3250,7 +3250,7 @@
         <v>0.05</v>
       </c>
       <c r="W12" t="n">
-        <v>1654</v>
+        <v>1658</v>
       </c>
       <c r="X12" t="n">
         <v>22.3</v>
@@ -3280,19 +3280,19 @@
         <v>14</v>
       </c>
       <c r="AG12" t="n">
-        <v>282.45</v>
+        <v>286.02</v>
       </c>
       <c r="AH12" t="n">
-        <v>202</v>
+        <v>203.02</v>
       </c>
       <c r="AI12" t="n">
-        <v>129.2</v>
+        <v>145.8</v>
       </c>
       <c r="AJ12" t="n">
         <v>217.7985916238683</v>
       </c>
       <c r="AK12" t="n">
-        <v>67.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
@@ -3436,13 +3436,13 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>69.43000000000001</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="J13" t="n">
         <v>64.48999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>7.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L13" t="n">
         <v>64.29000000000001</v>
@@ -3479,13 +3479,13 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>0.066</v>
+        <v>0.065</v>
       </c>
       <c r="W13" t="n">
-        <v>860</v>
+        <v>874</v>
       </c>
       <c r="X13" t="n">
-        <v>21.8</v>
+        <v>22.1</v>
       </c>
       <c r="Y13" t="n">
         <v>19</v>
@@ -3512,17 +3512,17 @@
         <v>12.14</v>
       </c>
       <c r="AG13" t="n">
-        <v>66.69</v>
+        <v>66.84</v>
       </c>
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="n">
-        <v>37.1</v>
+        <v>39.6</v>
       </c>
       <c r="AJ13" t="n">
         <v>64.49302166476625</v>
       </c>
       <c r="AK13" t="n">
-        <v>7.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
@@ -3666,13 +3666,13 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>99.25</v>
+        <v>99.56</v>
       </c>
       <c r="J14" t="n">
         <v>96.81999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="L14" t="n">
         <v>70.88</v>
@@ -3712,7 +3712,7 @@
         <v>0.5590000000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>2552</v>
+        <v>2553</v>
       </c>
       <c r="X14" t="n">
         <v>20.9</v>
@@ -3742,19 +3742,19 @@
         <v>30</v>
       </c>
       <c r="AG14" t="n">
-        <v>98.25</v>
+        <v>98.45</v>
       </c>
       <c r="AH14" t="n">
-        <v>92.61</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="AI14" t="n">
-        <v>15.9</v>
+        <v>17.6</v>
       </c>
       <c r="AJ14" t="n">
         <v>96.81860858409144</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
@@ -3898,13 +3898,13 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>92.39</v>
+        <v>91.41</v>
       </c>
       <c r="J15" t="n">
         <v>75.68000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>22.1</v>
+        <v>20.8</v>
       </c>
       <c r="L15" t="n">
         <v>74.84999999999999</v>
@@ -3941,13 +3941,13 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>0.131</v>
+        <v>0.132</v>
       </c>
       <c r="W15" t="n">
-        <v>2401</v>
+        <v>2387</v>
       </c>
       <c r="X15" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="Y15" t="n">
         <v>-3</v>
@@ -3974,19 +3974,19 @@
         <v>8</v>
       </c>
       <c r="AG15" t="n">
-        <v>75.67</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="AH15" t="n">
-        <v>49.86</v>
+        <v>50.09</v>
       </c>
       <c r="AI15" t="n">
-        <v>163</v>
+        <v>161.4</v>
       </c>
       <c r="AJ15" t="n">
         <v>75.6844038997483</v>
       </c>
       <c r="AK15" t="n">
-        <v>22.1</v>
+        <v>20.8</v>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
@@ -4101,16 +4101,16 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SILVERTUC</t>
+          <t>CHEMBONDCH</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
+          <t>CHEMBOND CHEMICALS LIMITED</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4118,40 +4118,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G16" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>131.18</v>
+        <v>247.47</v>
       </c>
       <c r="J16" t="n">
-        <v>171.54</v>
+        <v>243.52</v>
       </c>
       <c r="K16" t="n">
-        <v>-23.5</v>
+        <v>1.6</v>
       </c>
       <c r="L16" t="n">
-        <v>74.59</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="M16" t="n">
         <v>1.11</v>
       </c>
       <c r="N16" t="n">
-        <v>11081344</v>
+        <v>11080000</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>11081344</v>
+        <v>11080000</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -4165,124 +4165,124 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="V16" t="n">
-        <v>0.067</v>
+        <v>0.172</v>
       </c>
       <c r="W16" t="n">
-        <v>1642</v>
+        <v>646</v>
       </c>
       <c r="X16" t="n">
-        <v>37.7</v>
+        <v>54</v>
       </c>
       <c r="Y16" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="Z16" t="n">
-        <v>17</v>
+        <v>2.99</v>
       </c>
       <c r="AA16" t="n">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AC16" t="n">
-        <v>30.3</v>
+        <v>11.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>1</v>
       </c>
       <c r="AF16" t="n">
-        <v>23</v>
+        <v>16.21</v>
       </c>
       <c r="AG16" t="n">
-        <v>170.4</v>
+        <v>252.91</v>
       </c>
       <c r="AH16" t="n">
-        <v>467.19</v>
+        <v>192.08</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.4</v>
+        <v>60.6</v>
       </c>
       <c r="AJ16" t="n">
-        <v>171.5378328173375</v>
+        <v>243.5164835164835</v>
       </c>
       <c r="AK16" t="n">
-        <v>-23.5</v>
+        <v>1.6</v>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
+          <t>06-08-2026</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
           <t>25-08-2026</t>
         </is>
       </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>30-09-2026</t>
-        </is>
-      </c>
       <c r="AQ16" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="AR16" t="n">
+        <v>67</v>
+      </c>
+      <c r="AS16" t="n">
         <v>48</v>
       </c>
-      <c r="AS16" t="n">
-        <v>12</v>
-      </c>
       <c r="AT16" t="n">
         <v>0</v>
       </c>
       <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
         <v>1</v>
       </c>
-      <c r="AV16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>5</v>
-      </c>
       <c r="AX16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY16" t="n">
         <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>83720</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>83720</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>11081344</v>
+        <v>4065000</v>
       </c>
       <c r="BC16" t="n">
-        <v>11081344</v>
+        <v>11080000</v>
       </c>
       <c r="BD16" t="n">
         <v>0</v>
@@ -4318,10 +4318,10 @@
         <v>0</v>
       </c>
       <c r="BO16" t="n">
-        <v>83720</v>
+        <v>0</v>
       </c>
       <c r="BP16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ16" t="n">
         <v>0</v>
@@ -4333,16 +4333,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TAINWALCHM</t>
+          <t>SILVERTUC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
+          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -4350,40 +4350,40 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="G17" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>219.26</v>
+        <v>128.72</v>
       </c>
       <c r="J17" t="n">
-        <v>210.19</v>
+        <v>171.54</v>
       </c>
       <c r="K17" t="n">
-        <v>4.3</v>
+        <v>-25</v>
       </c>
       <c r="L17" t="n">
-        <v>67.04000000000001</v>
+        <v>74.59</v>
       </c>
       <c r="M17" t="n">
-        <v>0.62</v>
+        <v>1.11</v>
       </c>
       <c r="N17" t="n">
-        <v>6171564</v>
+        <v>11081344</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>6171564</v>
+        <v>11081344</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -4397,94 +4397,94 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>28-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
       <c r="V17" t="n">
-        <v>0.318</v>
+        <v>0.068</v>
       </c>
       <c r="W17" t="n">
-        <v>194</v>
+        <v>1630</v>
       </c>
       <c r="X17" t="n">
-        <v>24.1</v>
+        <v>37.4</v>
       </c>
       <c r="Y17" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>83</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>168.84</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>463.66</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>171.5378328173375</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>-25</v>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>25-08-2026</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>30-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS17" t="n">
         <v>12</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>7.91</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>209.44</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>197.87</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>210.188815475785</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>18-08-2026</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>28-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ17" t="n">
-        <v>41</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>55</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>14</v>
       </c>
       <c r="AT17" t="n">
         <v>0</v>
@@ -4493,28 +4493,28 @@
         <v>1</v>
       </c>
       <c r="AV17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW17" t="n">
         <v>5</v>
       </c>
-      <c r="AW17" t="n">
-        <v>14</v>
-      </c>
       <c r="AX17" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AY17" t="n">
         <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>131838</v>
+        <v>83720</v>
       </c>
       <c r="BA17" t="n">
-        <v>1936783</v>
+        <v>83720</v>
       </c>
       <c r="BB17" t="n">
-        <v>6171564</v>
+        <v>11081344</v>
       </c>
       <c r="BC17" t="n">
-        <v>6171564</v>
+        <v>11081344</v>
       </c>
       <c r="BD17" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
         <v>0</v>
       </c>
       <c r="BO17" t="n">
-        <v>1936783</v>
+        <v>83720</v>
       </c>
       <c r="BP17" t="n">
         <v>1</v>
@@ -4594,13 +4594,13 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>133.9</v>
+        <v>132.22</v>
       </c>
       <c r="J18" t="n">
         <v>143.72</v>
       </c>
       <c r="K18" t="n">
-        <v>-6.8</v>
+        <v>-8</v>
       </c>
       <c r="L18" t="n">
         <v>63.69</v>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>3.051</v>
+        <v>3.06</v>
       </c>
       <c r="W18" t="n">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="X18" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="Y18" t="n">
         <v>30</v>
@@ -4676,7 +4676,7 @@
         <v>143.7164139971926</v>
       </c>
       <c r="AK18" t="n">
-        <v>-6.8</v>
+        <v>-8</v>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
@@ -4791,16 +4791,16 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CHEMBONDCH</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CHEMBOND CHEMICALS LIMITED</t>
+          <t>OBCL LIMITED</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4808,141 +4808,139 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F19" t="n">
-        <v>14</v>
+        <v>-5</v>
       </c>
       <c r="G19" t="n">
+        <v>21</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>55.56</v>
+      </c>
+      <c r="J19" t="n">
+        <v>54.07</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L19" t="n">
+        <v>67.23</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N19" t="n">
+        <v>21953383</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>21953383</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
         <v>13</v>
       </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>220.86</v>
-      </c>
-      <c r="J19" t="n">
-        <v>243.52</v>
-      </c>
-      <c r="K19" t="n">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="L19" t="n">
-        <v>67.65000000000001</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N19" t="n">
-        <v>11080000</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>11080000</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S19" t="b">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3</v>
-      </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="V19" t="n">
-        <v>0.18</v>
+        <v>1.876</v>
       </c>
       <c r="W19" t="n">
-        <v>617</v>
-      </c>
-      <c r="X19" t="n">
-        <v>51.5</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="X19" t="inlineStr"/>
       <c r="Y19" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.99</v>
+        <v>2.47</v>
       </c>
       <c r="AA19" t="n">
-        <v>97</v>
+        <v>-3779</v>
       </c>
       <c r="AB19" t="n">
-        <v>1</v>
+        <v>-0.05</v>
       </c>
       <c r="AC19" t="n">
-        <v>11.6</v>
+        <v>-1.26</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AE19" t="b">
         <v>1</v>
       </c>
       <c r="AF19" t="n">
-        <v>16.21</v>
+        <v>3</v>
       </c>
       <c r="AG19" t="n">
-        <v>252.33</v>
+        <v>55.39</v>
       </c>
       <c r="AH19" t="n">
-        <v>191.63</v>
+        <v>55.25</v>
       </c>
       <c r="AI19" t="n">
-        <v>50.2</v>
+        <v>0.4</v>
       </c>
       <c r="AJ19" t="n">
-        <v>243.5164835164835</v>
+        <v>54.06877621438969</v>
       </c>
       <c r="AK19" t="n">
-        <v>-9.300000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>Aging</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="AQ19" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="AR19" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AS19" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="AT19" t="n">
         <v>0</v>
@@ -4951,67 +4949,67 @@
         <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>3285122</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>9524106</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>21953383</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>3285122</v>
+      </c>
+      <c r="BP19" t="n">
         <v>1</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>4065000</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>11080000</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>2</v>
       </c>
       <c r="BQ19" t="n">
         <v>0</v>
@@ -5052,13 +5050,13 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>471.9</v>
+        <v>470.2</v>
       </c>
       <c r="J20" t="n">
         <v>489.56</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.6</v>
+        <v>-4</v>
       </c>
       <c r="L20" t="n">
         <v>75</v>
@@ -5098,7 +5096,7 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>54686</v>
+        <v>54843</v>
       </c>
       <c r="X20" t="n">
         <v>46.4</v>
@@ -5128,19 +5126,19 @@
         <v>17</v>
       </c>
       <c r="AG20" t="n">
-        <v>493.49</v>
+        <v>492.46</v>
       </c>
       <c r="AH20" t="n">
-        <v>488.39</v>
+        <v>488.05</v>
       </c>
       <c r="AI20" t="n">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="AJ20" t="n">
         <v>489.5623319654733</v>
       </c>
       <c r="AK20" t="n">
-        <v>-3.6</v>
+        <v>-4</v>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
@@ -5284,13 +5282,13 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>212.86</v>
+        <v>210.75</v>
       </c>
       <c r="J21" t="n">
         <v>232.74</v>
       </c>
       <c r="K21" t="n">
-        <v>-8.5</v>
+        <v>-9.4</v>
       </c>
       <c r="L21" t="n">
         <v>67.13</v>
@@ -5330,10 +5328,10 @@
         <v>0.09</v>
       </c>
       <c r="W21" t="n">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="X21" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="Y21" t="n">
         <v>-5</v>
@@ -5360,19 +5358,19 @@
         <v>9</v>
       </c>
       <c r="AG21" t="n">
-        <v>226.38</v>
+        <v>226.18</v>
       </c>
       <c r="AH21" t="n">
-        <v>205.68</v>
+        <v>205.72</v>
       </c>
       <c r="AI21" t="n">
-        <v>10.8</v>
+        <v>11.1</v>
       </c>
       <c r="AJ21" t="n">
         <v>232.7375571148825</v>
       </c>
       <c r="AK21" t="n">
-        <v>-8.5</v>
+        <v>-9.4</v>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
@@ -5516,13 +5514,13 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>90.37</v>
+        <v>90.83</v>
       </c>
       <c r="J22" t="n">
         <v>68.68000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>31.6</v>
+        <v>32.3</v>
       </c>
       <c r="L22" t="n">
         <v>71.22</v>
@@ -5559,13 +5557,13 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>0.099</v>
+        <v>0.1</v>
       </c>
       <c r="W22" t="n">
-        <v>871</v>
+        <v>860</v>
       </c>
       <c r="X22" t="n">
-        <v>38</v>
+        <v>37.5</v>
       </c>
       <c r="Y22" t="n">
         <v>17</v>
@@ -5598,7 +5596,7 @@
         <v>68.68000000000001</v>
       </c>
       <c r="AK22" t="n">
-        <v>31.6</v>
+        <v>32.3</v>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
@@ -5742,13 +5740,13 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>115.81</v>
+        <v>118.12</v>
       </c>
       <c r="J23" t="n">
         <v>132.2</v>
       </c>
       <c r="K23" t="n">
-        <v>-12.4</v>
+        <v>-10.7</v>
       </c>
       <c r="L23" t="n">
         <v>67.83</v>
@@ -5785,13 +5783,13 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>1.078</v>
+        <v>1.066</v>
       </c>
       <c r="W23" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="X23" t="n">
-        <v>5.38</v>
+        <v>5.45</v>
       </c>
       <c r="Y23" t="n">
         <v>31</v>
@@ -5814,19 +5812,19 @@
       </c>
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="n">
-        <v>215.63</v>
+        <v>212.15</v>
       </c>
       <c r="AH23" t="n">
-        <v>263.57</v>
+        <v>262.84</v>
       </c>
       <c r="AI23" t="n">
-        <v>-56.5</v>
+        <v>-55.4</v>
       </c>
       <c r="AJ23" t="n">
         <v>132.2027333333333</v>
       </c>
       <c r="AK23" t="n">
-        <v>-12.4</v>
+        <v>-10.7</v>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
@@ -5941,16 +5939,16 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STEL</t>
+          <t>TAINWALCHM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>STEL HOLDINGS LIMITED</t>
+          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5958,10 +5956,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G24" t="n">
         <v>13</v>
@@ -5970,28 +5968,28 @@
         <v>-1</v>
       </c>
       <c r="I24" t="n">
-        <v>545.25</v>
+        <v>207.23</v>
       </c>
       <c r="J24" t="n">
-        <v>638.11</v>
+        <v>210.19</v>
       </c>
       <c r="K24" t="n">
-        <v>-14.6</v>
+        <v>-1.4</v>
       </c>
       <c r="L24" t="n">
-        <v>64.68000000000001</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>3.93</v>
+        <v>0.62</v>
       </c>
       <c r="N24" t="n">
-        <v>39342571</v>
+        <v>6171564</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>39342571</v>
+        <v>6171564</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -6005,7 +6003,7 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
@@ -6013,28 +6011,28 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>0.403</v>
+        <v>0.303</v>
       </c>
       <c r="W24" t="n">
-        <v>977</v>
+        <v>204</v>
       </c>
       <c r="X24" t="n">
-        <v>49.8</v>
+        <v>25.3</v>
       </c>
       <c r="Y24" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="Z24" t="n">
-        <v>-0.11</v>
+        <v>0.03</v>
       </c>
       <c r="AA24" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="AB24" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.58</v>
+        <v>7.91</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -6043,22 +6041,22 @@
         <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>-110</v>
+        <v>3.16</v>
       </c>
       <c r="AG24" t="n">
-        <v>594.36</v>
+        <v>209.59</v>
       </c>
       <c r="AH24" t="n">
-        <v>519.4</v>
+        <v>197.91</v>
       </c>
       <c r="AI24" t="n">
-        <v>12</v>
+        <v>12.6</v>
       </c>
       <c r="AJ24" t="n">
-        <v>638.108361041278</v>
+        <v>210.188815475785</v>
       </c>
       <c r="AK24" t="n">
-        <v>-14.6</v>
+        <v>-1.4</v>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
@@ -6077,7 +6075,7 @@
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>14-08-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
@@ -6086,10 +6084,10 @@
         </is>
       </c>
       <c r="AQ24" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="AR24" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="AS24" t="n">
         <v>14</v>
@@ -6101,28 +6099,28 @@
         <v>1</v>
       </c>
       <c r="AV24" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AW24" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="AX24" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="AY24" t="n">
         <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>779452</v>
+        <v>131838</v>
       </c>
       <c r="BA24" t="n">
-        <v>17574151</v>
+        <v>1936783</v>
       </c>
       <c r="BB24" t="n">
-        <v>39342571</v>
+        <v>6171564</v>
       </c>
       <c r="BC24" t="n">
-        <v>39342571</v>
+        <v>6171564</v>
       </c>
       <c r="BD24" t="n">
         <v>0</v>
@@ -6158,10 +6156,10 @@
         <v>0</v>
       </c>
       <c r="BO24" t="n">
-        <v>17574151</v>
+        <v>1936783</v>
       </c>
       <c r="BP24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ24" t="n">
         <v>0</v>
@@ -6173,12 +6171,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>WCIL</t>
+          <t>STEL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
+          <t>STEL HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -6190,10 +6188,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G25" t="n">
         <v>13</v>
@@ -6202,28 +6200,28 @@
         <v>-1</v>
       </c>
       <c r="I25" t="n">
-        <v>97.52</v>
+        <v>520.6</v>
       </c>
       <c r="J25" t="n">
-        <v>96.03</v>
+        <v>638.11</v>
       </c>
       <c r="K25" t="n">
-        <v>1.6</v>
+        <v>-18.4</v>
       </c>
       <c r="L25" t="n">
-        <v>71.89</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>2.6</v>
+        <v>3.93</v>
       </c>
       <c r="N25" t="n">
-        <v>26023230</v>
+        <v>39342571</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>26023230</v>
+        <v>39342571</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -6237,60 +6235,60 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>28-09-2026</t>
         </is>
       </c>
       <c r="V25" t="n">
-        <v>0.261</v>
+        <v>0.41</v>
       </c>
       <c r="W25" t="n">
-        <v>997</v>
+        <v>960</v>
       </c>
       <c r="X25" t="n">
-        <v>27.1</v>
+        <v>48.9</v>
       </c>
       <c r="Y25" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="Z25" t="n">
-        <v>18.68</v>
+        <v>-0.11</v>
       </c>
       <c r="AA25" t="n">
-        <v>-36</v>
+        <v>23</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.85</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AC25" t="n">
-        <v>6.83</v>
+        <v>1.58</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>4.02</v>
+        <v>-110</v>
       </c>
       <c r="AG25" t="n">
-        <v>89.18000000000001</v>
+        <v>593.5700000000001</v>
       </c>
       <c r="AH25" t="n">
-        <v>100.01</v>
+        <v>519.2</v>
       </c>
       <c r="AI25" t="n">
-        <v>4.4</v>
+        <v>9.5</v>
       </c>
       <c r="AJ25" t="n">
-        <v>96.02667896678967</v>
+        <v>638.108361041278</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.6</v>
+        <v>-18.4</v>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
@@ -6309,22 +6307,22 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>14-08-2026</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>28-09-2026</t>
         </is>
       </c>
       <c r="AQ25" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="AR25" t="n">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="AS25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT25" t="n">
         <v>0</v>
@@ -6333,28 +6331,28 @@
         <v>1</v>
       </c>
       <c r="AV25" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AW25" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="AX25" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="AY25" t="n">
         <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>6202680</v>
+        <v>779452</v>
       </c>
       <c r="BA25" t="n">
-        <v>26023230</v>
+        <v>17574151</v>
       </c>
       <c r="BB25" t="n">
-        <v>26023230</v>
+        <v>39342571</v>
       </c>
       <c r="BC25" t="n">
-        <v>26023230</v>
+        <v>39342571</v>
       </c>
       <c r="BD25" t="n">
         <v>0</v>
@@ -6390,10 +6388,10 @@
         <v>0</v>
       </c>
       <c r="BO25" t="n">
-        <v>26023230</v>
+        <v>17574151</v>
       </c>
       <c r="BP25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ25" t="n">
         <v>0</v>
@@ -6405,16 +6403,16 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GANESHCP</t>
+          <t>WCIL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
+          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -6422,171 +6420,171 @@
         </is>
       </c>
       <c r="E26" t="n">
+        <v>7</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>13</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>98.23</v>
+      </c>
+      <c r="J26" t="n">
+        <v>96.03</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L26" t="n">
+        <v>71.89</v>
+      </c>
+      <c r="M26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N26" t="n">
+        <v>26023230</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>26023230</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
         <v>3</v>
       </c>
-      <c r="F26" t="n">
-        <v>19</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>152.08</v>
-      </c>
-      <c r="J26" t="n">
-        <v>166</v>
-      </c>
-      <c r="K26" t="n">
-        <v>-8.4</v>
-      </c>
-      <c r="L26" t="n">
-        <v>64.08</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N26" t="n">
-        <v>8001009</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>8001009</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S26" t="b">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2</v>
-      </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="V26" t="n">
-        <v>0.127</v>
+        <v>0.26</v>
       </c>
       <c r="W26" t="n">
-        <v>632</v>
+        <v>999</v>
       </c>
       <c r="X26" t="n">
-        <v>13.9</v>
+        <v>27.2</v>
       </c>
       <c r="Y26" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z26" t="n">
-        <v>21</v>
+        <v>18.68</v>
       </c>
       <c r="AA26" t="n">
-        <v>45</v>
+        <v>-36</v>
       </c>
       <c r="AB26" t="n">
-        <v>3.1</v>
+        <v>0.85</v>
       </c>
       <c r="AC26" t="n">
-        <v>19.3</v>
+        <v>6.83</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>89.36</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>96.02667896678967</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>18-09-2026</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>29-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
         <v>1</v>
       </c>
-      <c r="AF26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>163.84</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>186.6</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>-25.5</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>165.9960373443983</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>-8.4</v>
-      </c>
-      <c r="AL26" t="inlineStr">
-        <is>
-          <t>Aging</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Mature Accumulation</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>Mature — Wait for Pullback</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>25-08-2026</t>
-        </is>
-      </c>
-      <c r="AP26" t="inlineStr">
-        <is>
-          <t>02-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ26" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>48</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>0</v>
-      </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY26" t="n">
         <v>0</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>6202680</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>26023230</v>
       </c>
       <c r="BB26" t="n">
-        <v>8001009</v>
+        <v>26023230</v>
       </c>
       <c r="BC26" t="n">
-        <v>8001009</v>
+        <v>26023230</v>
       </c>
       <c r="BD26" t="n">
         <v>0</v>
@@ -6622,7 +6620,7 @@
         <v>0</v>
       </c>
       <c r="BO26" t="n">
-        <v>0</v>
+        <v>26023230</v>
       </c>
       <c r="BP26" t="n">
         <v>1</v>
@@ -6637,16 +6635,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SINCLAIR</t>
+          <t>GANESHCP</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SINCLAIRS HOTELS LIMITED</t>
+          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6654,141 +6652,141 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F27" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="G27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>74.45999999999999</v>
+        <v>155.7</v>
       </c>
       <c r="J27" t="n">
-        <v>81.09999999999999</v>
+        <v>166</v>
       </c>
       <c r="K27" t="n">
-        <v>-8.199999999999999</v>
+        <v>-6.2</v>
       </c>
       <c r="L27" t="n">
-        <v>62.78</v>
+        <v>64.08</v>
       </c>
       <c r="M27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N27" t="n">
+        <v>8001009</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>8001009</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
         <v>2</v>
       </c>
-      <c r="N27" t="n">
-        <v>19959718</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>19959718</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S27" t="b">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>8</v>
-      </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="V27" t="n">
-        <v>0.517</v>
+        <v>0.127</v>
       </c>
       <c r="W27" t="n">
-        <v>386</v>
+        <v>630</v>
       </c>
       <c r="X27" t="n">
-        <v>35.8</v>
+        <v>13.9</v>
       </c>
       <c r="Y27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z27" t="n">
         <v>21</v>
       </c>
-      <c r="Z27" t="n">
-        <v>8.390000000000001</v>
-      </c>
       <c r="AA27" t="n">
-        <v>-19</v>
+        <v>45</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.54</v>
+        <v>3.1</v>
       </c>
       <c r="AC27" t="n">
-        <v>8.73</v>
+        <v>19.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.28</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AE27" t="b">
         <v>1</v>
       </c>
       <c r="AF27" t="n">
-        <v>41.64</v>
+        <v>11</v>
       </c>
       <c r="AG27" t="n">
-        <v>78.09999999999999</v>
+        <v>163.68</v>
       </c>
       <c r="AH27" t="n">
-        <v>77.54000000000001</v>
+        <v>186.21</v>
       </c>
       <c r="AI27" t="n">
-        <v>-4.5</v>
+        <v>-20.4</v>
       </c>
       <c r="AJ27" t="n">
-        <v>81.10277768748172</v>
+        <v>165.9960373443983</v>
       </c>
       <c r="AK27" t="n">
-        <v>-8.199999999999999</v>
+        <v>-6.2</v>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="AQ27" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="AR27" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="AS27" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="AT27" t="n">
         <v>0</v>
@@ -6797,13 +6795,13 @@
         <v>0</v>
       </c>
       <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
         <v>2</v>
       </c>
-      <c r="AW27" t="n">
-        <v>8</v>
-      </c>
       <c r="AX27" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AY27" t="n">
         <v>0</v>
@@ -6812,13 +6810,13 @@
         <v>0</v>
       </c>
       <c r="BA27" t="n">
-        <v>2802843</v>
+        <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>19959718</v>
+        <v>8001009</v>
       </c>
       <c r="BC27" t="n">
-        <v>19959718</v>
+        <v>8001009</v>
       </c>
       <c r="BD27" t="n">
         <v>0</v>
@@ -6854,7 +6852,7 @@
         <v>0</v>
       </c>
       <c r="BO27" t="n">
-        <v>2802843</v>
+        <v>0</v>
       </c>
       <c r="BP27" t="n">
         <v>1</v>
@@ -6869,16 +6867,16 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>SINCLAIR</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>OBCL LIMITED</t>
+          <t>SINCLAIRS HOTELS LIMITED</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -6886,105 +6884,107 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F28" t="n">
-        <v>-5</v>
+        <v>8</v>
       </c>
       <c r="G28" t="n">
+        <v>4</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>74.16</v>
+      </c>
+      <c r="J28" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-8.6</v>
+      </c>
+      <c r="L28" t="n">
+        <v>62.78</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2</v>
+      </c>
+      <c r="N28" t="n">
+        <v>19959718</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>19959718</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
         <v>8</v>
       </c>
-      <c r="H28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I28" t="n">
-        <v>55.19</v>
-      </c>
-      <c r="J28" t="n">
-        <v>54.07</v>
-      </c>
-      <c r="K28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="L28" t="n">
-        <v>67.23</v>
-      </c>
-      <c r="M28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="N28" t="n">
-        <v>21953383</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>21953383</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S28" t="b">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>13</v>
-      </c>
       <c r="U28" t="inlineStr">
         <is>
           <t>24-09-2026</t>
         </is>
       </c>
       <c r="V28" t="n">
-        <v>1.876</v>
+        <v>0.525</v>
       </c>
       <c r="W28" t="n">
-        <v>117</v>
-      </c>
-      <c r="X28" t="inlineStr"/>
+        <v>380</v>
+      </c>
+      <c r="X28" t="n">
+        <v>35.2</v>
+      </c>
       <c r="Y28" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.47</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="AA28" t="n">
-        <v>-3779</v>
+        <v>-19</v>
       </c>
       <c r="AB28" t="n">
-        <v>-0.05</v>
+        <v>1.54</v>
       </c>
       <c r="AC28" t="n">
-        <v>-1.26</v>
+        <v>8.73</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.8</v>
+        <v>0.28</v>
       </c>
       <c r="AE28" t="b">
         <v>1</v>
       </c>
       <c r="AF28" t="n">
-        <v>3</v>
+        <v>41.64</v>
       </c>
       <c r="AG28" t="n">
-        <v>55.33</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="AH28" t="n">
-        <v>55.25</v>
+        <v>77.48999999999999</v>
       </c>
       <c r="AI28" t="n">
-        <v>-1</v>
+        <v>-5.2</v>
       </c>
       <c r="AJ28" t="n">
-        <v>54.06877621438969</v>
+        <v>81.10277768748172</v>
       </c>
       <c r="AK28" t="n">
-        <v>2.1</v>
+        <v>-8.6</v>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
@@ -7012,10 +7012,10 @@
         </is>
       </c>
       <c r="AQ28" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="AR28" t="n">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="AS28" t="n">
         <v>18</v>
@@ -7027,13 +7027,13 @@
         <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX28" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AY28" t="n">
         <v>0</v>
@@ -7042,13 +7042,13 @@
         <v>0</v>
       </c>
       <c r="BA28" t="n">
-        <v>3285122</v>
+        <v>2802843</v>
       </c>
       <c r="BB28" t="n">
-        <v>9524106</v>
+        <v>19959718</v>
       </c>
       <c r="BC28" t="n">
-        <v>21953383</v>
+        <v>19959718</v>
       </c>
       <c r="BD28" t="n">
         <v>0</v>
@@ -7084,7 +7084,7 @@
         <v>0</v>
       </c>
       <c r="BO28" t="n">
-        <v>3285122</v>
+        <v>2802843</v>
       </c>
       <c r="BP28" t="n">
         <v>1</v>
@@ -7108,7 +7108,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -7122,19 +7122,19 @@
         <v>16</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>414.5</v>
+        <v>422.3</v>
       </c>
       <c r="J29" t="n">
         <v>417.34</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.7</v>
+        <v>1.2</v>
       </c>
       <c r="L29" t="n">
         <v>61.75</v>
@@ -7171,13 +7171,13 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>0.041</v>
+        <v>0.042</v>
       </c>
       <c r="W29" t="n">
-        <v>1672</v>
+        <v>1666</v>
       </c>
       <c r="X29" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="Y29" t="n">
         <v>10</v>
@@ -7204,19 +7204,19 @@
         <v>12</v>
       </c>
       <c r="AG29" t="n">
-        <v>427.17</v>
+        <v>426.79</v>
       </c>
       <c r="AH29" t="n">
-        <v>472.98</v>
+        <v>472.38</v>
       </c>
       <c r="AI29" t="n">
-        <v>-8.5</v>
+        <v>-5.9</v>
       </c>
       <c r="AJ29" t="n">
         <v>417.3421638870492</v>
       </c>
       <c r="AK29" t="n">
-        <v>-0.7</v>
+        <v>1.2</v>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
@@ -7360,13 +7360,13 @@
         <v>-1</v>
       </c>
       <c r="I30" t="n">
-        <v>159.8</v>
+        <v>165.04</v>
       </c>
       <c r="J30" t="n">
         <v>174.27</v>
       </c>
       <c r="K30" t="n">
-        <v>-8.300000000000001</v>
+        <v>-5.3</v>
       </c>
       <c r="L30" t="n">
         <v>61.48</v>
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>0.504</v>
+        <v>0.514</v>
       </c>
       <c r="W30" t="n">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="X30" t="n">
-        <v>36.9</v>
+        <v>36.2</v>
       </c>
       <c r="Y30" t="n">
         <v>-44</v>
@@ -7436,19 +7436,19 @@
         <v>-35.96</v>
       </c>
       <c r="AG30" t="n">
-        <v>170.56</v>
+        <v>170.22</v>
       </c>
       <c r="AH30" t="n">
-        <v>176.96</v>
+        <v>176.76</v>
       </c>
       <c r="AI30" t="n">
-        <v>-4.4</v>
+        <v>-1.8</v>
       </c>
       <c r="AJ30" t="n">
         <v>174.2652478588113</v>
       </c>
       <c r="AK30" t="n">
-        <v>-8.300000000000001</v>
+        <v>-5.3</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
@@ -7592,13 +7592,13 @@
         <v>-1</v>
       </c>
       <c r="I31" t="n">
-        <v>23.59</v>
+        <v>24.08</v>
       </c>
       <c r="J31" t="n">
         <v>27.53</v>
       </c>
       <c r="K31" t="n">
-        <v>-14.3</v>
+        <v>-12.5</v>
       </c>
       <c r="L31" t="n">
         <v>61.81</v>
@@ -7635,10 +7635,10 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>0.255</v>
+        <v>0.254</v>
       </c>
       <c r="W31" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="X31" t="n">
         <v>13.4</v>
@@ -7668,19 +7668,19 @@
         <v>1.83</v>
       </c>
       <c r="AG31" t="n">
-        <v>27.29</v>
+        <v>27.2</v>
       </c>
       <c r="AH31" t="n">
-        <v>31.57</v>
+        <v>31.5</v>
       </c>
       <c r="AI31" t="n">
-        <v>-15.7</v>
+        <v>-16.5</v>
       </c>
       <c r="AJ31" t="n">
         <v>27.53361702127659</v>
       </c>
       <c r="AK31" t="n">
-        <v>-14.3</v>
+        <v>-12.5</v>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
@@ -7795,12 +7795,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DANGEE</t>
+          <t>TRUALT</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Dangee Dums Limited</t>
+          <t>TRUALT BIOENERGY LIMITED</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -7812,165 +7812,171 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F32" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G32" t="n">
+        <v>25</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-16</v>
+      </c>
+      <c r="I32" t="n">
+        <v>443.25</v>
+      </c>
+      <c r="J32" t="n">
+        <v>349.57</v>
+      </c>
+      <c r="K32" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="L32" t="n">
+        <v>70.55</v>
+      </c>
+      <c r="M32" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="N32" t="n">
+        <v>315995536</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>315995536</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>11</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>30-09-2026</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="W32" t="n">
+        <v>3804</v>
+      </c>
+      <c r="X32" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>127</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-14</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>442.58</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>433.55</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>349.5746258337085</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN32" t="inlineStr">
+        <is>
+          <t>Late — Poor Entry</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>05-08-2026</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>30-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ32" t="n">
+        <v>56</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>68</v>
+      </c>
+      <c r="AS32" t="n">
         <v>12</v>
       </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K32" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="L32" t="n">
-        <v>64.45</v>
-      </c>
-      <c r="M32" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="N32" t="n">
-        <v>20159573</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>20159573</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S32" t="b">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>1</v>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>24-09-2026</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>-86</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>14.22</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>2.817550384346611</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Mature Accumulation</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>Mature — Wait for Pullback</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>24-09-2026</t>
-        </is>
-      </c>
-      <c r="AP32" t="inlineStr">
-        <is>
-          <t>24-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>18</v>
-      </c>
       <c r="AT32" t="n">
         <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV32" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AW32" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AX32" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AY32" t="n">
         <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>55737360</v>
       </c>
       <c r="BA32" t="n">
-        <v>20159573</v>
+        <v>213764633</v>
       </c>
       <c r="BB32" t="n">
-        <v>20159573</v>
+        <v>213764633</v>
       </c>
       <c r="BC32" t="n">
-        <v>20159573</v>
+        <v>315995536</v>
       </c>
       <c r="BD32" t="n">
         <v>0</v>
@@ -8006,7 +8012,7 @@
         <v>0</v>
       </c>
       <c r="BO32" t="n">
-        <v>20159573</v>
+        <v>213764633</v>
       </c>
       <c r="BP32" t="n">
         <v>1</v>
@@ -8021,16 +8027,16 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>LAOPALA</t>
+          <t>AVONMORE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LA OPALA RG LIMITED</t>
+          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -8038,40 +8044,40 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" t="n">
         <v>5</v>
       </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I33" t="n">
-        <v>154.76</v>
+        <v>12.76</v>
       </c>
       <c r="J33" t="n">
-        <v>159.62</v>
+        <v>12.86</v>
       </c>
       <c r="K33" t="n">
-        <v>-3</v>
+        <v>-0.8</v>
       </c>
       <c r="L33" t="n">
-        <v>65.64</v>
+        <v>69.12</v>
       </c>
       <c r="M33" t="n">
-        <v>3.99</v>
+        <v>2.35</v>
       </c>
       <c r="N33" t="n">
-        <v>39906048</v>
+        <v>23479616</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>39906048</v>
+        <v>23479616</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -8085,60 +8091,56 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>17-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="V33" t="n">
-        <v>0.236</v>
+        <v>0.652</v>
       </c>
       <c r="W33" t="n">
-        <v>1690</v>
+        <v>360</v>
       </c>
       <c r="X33" t="n">
-        <v>17.9</v>
+        <v>1162</v>
       </c>
       <c r="Y33" t="n">
-        <v>-3</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>26</v>
-      </c>
+        <v>-61</v>
+      </c>
+      <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="n">
-        <v>-4</v>
+        <v>-98</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.36</v>
+        <v>0.01</v>
       </c>
       <c r="AC33" t="n">
-        <v>14.2</v>
+        <v>2.46</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.01</v>
+        <v>0.44</v>
       </c>
       <c r="AE33" t="b">
         <v>1</v>
       </c>
-      <c r="AF33" t="n">
-        <v>36</v>
-      </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="n">
-        <v>172.06</v>
+        <v>12.8</v>
       </c>
       <c r="AH33" t="n">
-        <v>183.3</v>
+        <v>12.93</v>
       </c>
       <c r="AI33" t="n">
-        <v>-11.1</v>
+        <v>7.3</v>
       </c>
       <c r="AJ33" t="n">
-        <v>159.624192</v>
+        <v>12.85608234597773</v>
       </c>
       <c r="AK33" t="n">
-        <v>-3</v>
+        <v>-0.7</v>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
@@ -8157,38 +8159,38 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>17-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="AQ33" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="AR33" t="n">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="AS33" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX33" t="n">
         <v>25</v>
       </c>
-      <c r="AT33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>2</v>
-      </c>
       <c r="AY33" t="n">
         <v>0</v>
       </c>
@@ -8196,13 +8198,13 @@
         <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>39906048</v>
+        <v>2496337</v>
       </c>
       <c r="BB33" t="n">
-        <v>39906048</v>
+        <v>16559572</v>
       </c>
       <c r="BC33" t="n">
-        <v>39906048</v>
+        <v>23479616</v>
       </c>
       <c r="BD33" t="n">
         <v>0</v>
@@ -8238,7 +8240,7 @@
         <v>0</v>
       </c>
       <c r="BO33" t="n">
-        <v>39906048</v>
+        <v>2496337</v>
       </c>
       <c r="BP33" t="n">
         <v>1</v>
@@ -8253,12 +8255,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>LAOPALA</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ENVIRO INFRA ENGINEERS LIMITED</t>
+          <t>LA OPALA RG LIMITED</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -8270,156 +8272,156 @@
         </is>
       </c>
       <c r="E34" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" t="n">
+        <v>5</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>151.9</v>
+      </c>
+      <c r="J34" t="n">
+        <v>159.62</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="L34" t="n">
+        <v>65.64</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="N34" t="n">
+        <v>39906048</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>39906048</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
         <v>2</v>
       </c>
-      <c r="F34" t="n">
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>17-09-2026</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1685</v>
+      </c>
+      <c r="X34" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AE34" t="b">
         <v>1</v>
       </c>
-      <c r="G34" t="n">
-        <v>9</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>179.96</v>
-      </c>
-      <c r="J34" t="n">
-        <v>191.87</v>
-      </c>
-      <c r="K34" t="n">
-        <v>-6.2</v>
-      </c>
-      <c r="L34" t="n">
-        <v>70.02</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="N34" t="n">
-        <v>13430794</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>13430794</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S34" t="b">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>3</v>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>02-09-2026</t>
-        </is>
-      </c>
-      <c r="V34" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="W34" t="n">
-        <v>3149</v>
-      </c>
-      <c r="X34" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>-4</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>51</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>-9</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AE34" t="b">
-        <v>0</v>
-      </c>
       <c r="AF34" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="AG34" t="n">
-        <v>200.11</v>
+        <v>171.39</v>
       </c>
       <c r="AH34" t="n">
-        <v>192.96</v>
+        <v>183.04</v>
       </c>
       <c r="AI34" t="n">
-        <v>5.2</v>
+        <v>-12.2</v>
       </c>
       <c r="AJ34" t="n">
-        <v>191.8684857142857</v>
+        <v>159.624192</v>
       </c>
       <c r="AK34" t="n">
-        <v>-6.2</v>
+        <v>-4.8</v>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>Aging</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
       <c r="AQ34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
         <v>2</v>
       </c>
-      <c r="AR34" t="n">
-        <v>42</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>0</v>
-      </c>
       <c r="AW34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY34" t="n">
         <v>0</v>
@@ -8428,13 +8430,13 @@
         <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>39906048</v>
       </c>
       <c r="BB34" t="n">
-        <v>13430794</v>
+        <v>39906048</v>
       </c>
       <c r="BC34" t="n">
-        <v>13430794</v>
+        <v>39906048</v>
       </c>
       <c r="BD34" t="n">
         <v>0</v>
@@ -8470,10 +8472,10 @@
         <v>0</v>
       </c>
       <c r="BO34" t="n">
-        <v>0</v>
+        <v>39906048</v>
       </c>
       <c r="BP34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ34" t="n">
         <v>0</v>
@@ -8485,124 +8487,124 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GOKUL</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
+          <t>ENVIRO INFRA ENGINEERS LIMITED</t>
         </is>
       </c>
       <c r="C35" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="n">
+        <v>9</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>178.87</v>
+      </c>
+      <c r="J35" t="n">
+        <v>191.87</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="L35" t="n">
+        <v>70.02</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="N35" t="n">
+        <v>13430794</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>13430794</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
         <v>3</v>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>5</v>
-      </c>
-      <c r="F35" t="n">
-        <v>4</v>
-      </c>
-      <c r="G35" t="n">
-        <v>4</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-2</v>
-      </c>
-      <c r="I35" t="n">
-        <v>38.05</v>
-      </c>
-      <c r="J35" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="K35" t="n">
-        <v>-10.7</v>
-      </c>
-      <c r="L35" t="n">
-        <v>71.79000000000001</v>
-      </c>
-      <c r="M35" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N35" t="n">
-        <v>13998766</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>13998766</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S35" t="b">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>12</v>
-      </c>
       <c r="U35" t="inlineStr">
         <is>
           <t>02-09-2026</t>
         </is>
       </c>
       <c r="V35" t="n">
-        <v>0.37</v>
+        <v>0.043</v>
       </c>
       <c r="W35" t="n">
-        <v>378</v>
+        <v>3142</v>
       </c>
       <c r="X35" t="n">
-        <v>93.59999999999999</v>
+        <v>18.6</v>
       </c>
       <c r="Y35" t="n">
-        <v>246</v>
+        <v>-4</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.91</v>
+        <v>51</v>
       </c>
       <c r="AA35" t="n">
-        <v>10</v>
+        <v>-9</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.14</v>
+        <v>2.04</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.07</v>
+        <v>20.8</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>4.21</v>
+        <v>21</v>
       </c>
       <c r="AG35" t="n">
-        <v>40.47</v>
+        <v>199.41</v>
       </c>
       <c r="AH35" t="n">
-        <v>39.74</v>
+        <v>192.86</v>
       </c>
       <c r="AI35" t="n">
-        <v>-4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AJ35" t="n">
-        <v>42.60032805144139</v>
+        <v>191.8684857142857</v>
       </c>
       <c r="AK35" t="n">
-        <v>-10.7</v>
+        <v>-6.8</v>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
@@ -8621,7 +8623,7 @@
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
@@ -8630,10 +8632,10 @@
         </is>
       </c>
       <c r="AQ35" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AR35" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="AS35" t="n">
         <v>40</v>
@@ -8648,10 +8650,10 @@
         <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AX35" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AY35" t="n">
         <v>0</v>
@@ -8663,10 +8665,10 @@
         <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>13998766</v>
+        <v>13430794</v>
       </c>
       <c r="BC35" t="n">
-        <v>13998766</v>
+        <v>13430794</v>
       </c>
       <c r="BD35" t="n">
         <v>0</v>
@@ -8705,7 +8707,7 @@
         <v>0</v>
       </c>
       <c r="BP35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ35" t="n">
         <v>0</v>
@@ -8717,16 +8719,16 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AVONMORE</t>
+          <t>GOKUL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
+          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -8734,40 +8736,40 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H36" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="I36" t="n">
-        <v>12.3</v>
+        <v>38.04</v>
       </c>
       <c r="J36" t="n">
-        <v>12.86</v>
+        <v>42.6</v>
       </c>
       <c r="K36" t="n">
-        <v>-4.4</v>
+        <v>-10.7</v>
       </c>
       <c r="L36" t="n">
-        <v>69.12</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>2.35</v>
+        <v>1.4</v>
       </c>
       <c r="N36" t="n">
-        <v>23479616</v>
+        <v>13998766</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>23479616</v>
+        <v>13998766</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -8781,90 +8783,94 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="V36" t="n">
-        <v>0.64</v>
+        <v>0.376</v>
       </c>
       <c r="W36" t="n">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="X36" t="n">
-        <v>1183</v>
+        <v>92.2</v>
       </c>
       <c r="Y36" t="n">
-        <v>-61</v>
-      </c>
-      <c r="Z36" t="inlineStr"/>
+        <v>246</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0.91</v>
+      </c>
       <c r="AA36" t="n">
-        <v>-98</v>
+        <v>10</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.01</v>
+        <v>0.14</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.46</v>
+        <v>2.07</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF36" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>4.21</v>
+      </c>
       <c r="AG36" t="n">
-        <v>12.77</v>
+        <v>40.44</v>
       </c>
       <c r="AH36" t="n">
-        <v>12.95</v>
+        <v>39.74</v>
       </c>
       <c r="AI36" t="n">
-        <v>-1.2</v>
+        <v>-2.6</v>
       </c>
       <c r="AJ36" t="n">
-        <v>12.85608234597773</v>
+        <v>42.60032805144139</v>
       </c>
       <c r="AK36" t="n">
-        <v>-4.3</v>
+        <v>-10.7</v>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>10-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="AQ36" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="AR36" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="AS36" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="AT36" t="n">
         <v>0</v>
@@ -8873,13 +8879,13 @@
         <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AX36" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AY36" t="n">
         <v>0</v>
@@ -8888,13 +8894,13 @@
         <v>0</v>
       </c>
       <c r="BA36" t="n">
-        <v>2496337</v>
+        <v>0</v>
       </c>
       <c r="BB36" t="n">
-        <v>16559572</v>
+        <v>13998766</v>
       </c>
       <c r="BC36" t="n">
-        <v>23479616</v>
+        <v>13998766</v>
       </c>
       <c r="BD36" t="n">
         <v>0</v>
@@ -8930,7 +8936,7 @@
         <v>0</v>
       </c>
       <c r="BO36" t="n">
-        <v>2496337</v>
+        <v>0</v>
       </c>
       <c r="BP36" t="n">
         <v>1</v>
@@ -8945,16 +8951,16 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>DANGEE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TRUALT BIOENERGY LIMITED</t>
+          <t>Dangee Dums Limited</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -8962,40 +8968,40 @@
         </is>
       </c>
       <c r="E37" t="n">
+        <v>3</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G37" t="n">
         <v>8</v>
       </c>
-      <c r="F37" t="n">
-        <v>-3</v>
-      </c>
-      <c r="G37" t="n">
-        <v>17</v>
-      </c>
       <c r="H37" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>427.2</v>
+        <v>3.13</v>
       </c>
       <c r="J37" t="n">
-        <v>349.57</v>
+        <v>2.82</v>
       </c>
       <c r="K37" t="n">
-        <v>22.2</v>
+        <v>11</v>
       </c>
       <c r="L37" t="n">
-        <v>70.55</v>
+        <v>64.45</v>
       </c>
       <c r="M37" t="n">
-        <v>31.6</v>
+        <v>2.02</v>
       </c>
       <c r="N37" t="n">
-        <v>315995536</v>
+        <v>20159573</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>315995536</v>
+        <v>20159573</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -9009,60 +9015,54 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
-        </is>
-      </c>
-      <c r="V37" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="W37" t="n">
-        <v>3786</v>
-      </c>
-      <c r="X37" t="n">
-        <v>26.5</v>
-      </c>
+          <t>24-09-2026</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
       <c r="Y37" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Z37" t="n">
-        <v>127</v>
+        <v>0.98</v>
       </c>
       <c r="AA37" t="n">
-        <v>-14</v>
+        <v>-86</v>
       </c>
       <c r="AB37" t="n">
-        <v>6.41</v>
+        <v>-0.03</v>
       </c>
       <c r="AC37" t="n">
-        <v>9.890000000000001</v>
+        <v>2.27</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.05</v>
+        <v>1.58</v>
       </c>
       <c r="AE37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF37" t="n">
-        <v>21</v>
+        <v>14.22</v>
       </c>
       <c r="AG37" t="n">
-        <v>442.44</v>
+        <v>2.91</v>
       </c>
       <c r="AH37" t="n">
-        <v>433.38</v>
+        <v>3.16</v>
       </c>
       <c r="AI37" t="n">
-        <v>2.7</v>
+        <v>-0.3</v>
       </c>
       <c r="AJ37" t="n">
-        <v>349.5746258337085</v>
+        <v>2.817550384346611</v>
       </c>
       <c r="AK37" t="n">
-        <v>22.2</v>
+        <v>11.1</v>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
@@ -9071,62 +9071,62 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="AQ37" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="AR37" t="n">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="AS37" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AT37" t="n">
         <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AW37" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AX37" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="AY37" t="n">
         <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>55737360</v>
+        <v>0</v>
       </c>
       <c r="BA37" t="n">
-        <v>213764633</v>
+        <v>20159573</v>
       </c>
       <c r="BB37" t="n">
-        <v>213764633</v>
+        <v>20159573</v>
       </c>
       <c r="BC37" t="n">
-        <v>315995536</v>
+        <v>20159573</v>
       </c>
       <c r="BD37" t="n">
         <v>0</v>
@@ -9162,7 +9162,7 @@
         <v>0</v>
       </c>
       <c r="BO37" t="n">
-        <v>213764633</v>
+        <v>20159573</v>
       </c>
       <c r="BP37" t="n">
         <v>1</v>
@@ -9206,13 +9206,13 @@
         <v>-13</v>
       </c>
       <c r="I38" t="n">
-        <v>764.8</v>
+        <v>781.1</v>
       </c>
       <c r="J38" t="n">
         <v>726.25</v>
       </c>
       <c r="K38" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="L38" t="n">
         <v>71.92</v>
@@ -9252,10 +9252,10 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>5337</v>
+        <v>5361</v>
       </c>
       <c r="X38" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="Y38" t="n">
         <v>26</v>
@@ -9282,19 +9282,19 @@
         <v>25</v>
       </c>
       <c r="AG38" t="n">
-        <v>706.3</v>
+        <v>710.16</v>
       </c>
       <c r="AH38" t="n">
-        <v>494.13</v>
+        <v>496.23</v>
       </c>
       <c r="AI38" t="n">
-        <v>126.6</v>
+        <v>132.9</v>
       </c>
       <c r="AJ38" t="n">
         <v>726.2520355006753</v>
       </c>
       <c r="AK38" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
@@ -9409,16 +9409,16 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>INDIQUBE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>U. Y. Fincorp Limited</t>
+          <t>Indiqube Spaces Limited</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -9429,37 +9429,37 @@
         <v>3</v>
       </c>
       <c r="F39" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G39" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>24.76</v>
+        <v>191.7</v>
       </c>
       <c r="J39" t="n">
-        <v>21.01</v>
+        <v>195.05</v>
       </c>
       <c r="K39" t="n">
-        <v>17.8</v>
+        <v>-1.7</v>
       </c>
       <c r="L39" t="n">
-        <v>70.87</v>
+        <v>60.6</v>
       </c>
       <c r="M39" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="N39" t="n">
-        <v>4960333</v>
+        <v>4486152</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>4960333</v>
+        <v>4486152</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -9473,90 +9473,92 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
+        <v>4</v>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>25-09-2026</t>
+        </is>
+      </c>
+      <c r="V39" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="W39" t="n">
+        <v>4051</v>
+      </c>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="n">
+        <v>39</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>258</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>61</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>191.33</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>176.53</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>195.0500869565217</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="AL39" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN39" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>22-09-2026</t>
+        </is>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>25-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ39" t="n">
         <v>3</v>
       </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>19-08-2026</t>
-        </is>
-      </c>
-      <c r="V39" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="W39" t="n">
-        <v>490</v>
-      </c>
-      <c r="X39" t="n">
-        <v>7.92</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>118</v>
-      </c>
-      <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="n">
-        <v>391</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="inlineStr"/>
-      <c r="AG39" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>15.86</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>80.7</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>21.00741139152052</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="AL39" t="inlineStr">
-        <is>
-          <t>Aging</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Mature Accumulation</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>Mature — Wait for Pullback</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>17-08-2026</t>
-        </is>
-      </c>
-      <c r="AP39" t="inlineStr">
-        <is>
-          <t>19-08-2026</t>
-        </is>
-      </c>
-      <c r="AQ39" t="n">
-        <v>2</v>
-      </c>
       <c r="AR39" t="n">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="AS39" t="n">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="AT39" t="n">
         <v>0</v>
@@ -9565,13 +9567,13 @@
         <v>0</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AW39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY39" t="n">
         <v>0</v>
@@ -9580,13 +9582,13 @@
         <v>0</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>4486152</v>
       </c>
       <c r="BB39" t="n">
-        <v>4960333</v>
+        <v>4486152</v>
       </c>
       <c r="BC39" t="n">
-        <v>4960333</v>
+        <v>4486152</v>
       </c>
       <c r="BD39" t="n">
         <v>0</v>
@@ -9622,7 +9624,7 @@
         <v>0</v>
       </c>
       <c r="BO39" t="n">
-        <v>0</v>
+        <v>4486152</v>
       </c>
       <c r="BP39" t="n">
         <v>1</v>
@@ -9637,57 +9639,57 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>INDIQUBE</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Indiqube Spaces Limited</t>
+          <t>U. Y. Fincorp Limited</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Fundamental Watch</t>
+          <t>Avoid</t>
         </is>
       </c>
       <c r="E40" t="n">
         <v>3</v>
       </c>
       <c r="F40" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G40" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>194.47</v>
+        <v>25.88</v>
       </c>
       <c r="J40" t="n">
-        <v>195.05</v>
+        <v>21.01</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.3</v>
+        <v>23.2</v>
       </c>
       <c r="L40" t="n">
-        <v>60.6</v>
+        <v>70.87</v>
       </c>
       <c r="M40" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="N40" t="n">
-        <v>4486152</v>
+        <v>4960333</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>4486152</v>
+        <v>4960333</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -9701,107 +9703,105 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>25-09-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="V40" t="n">
-        <v>0.011</v>
+        <v>0.1</v>
       </c>
       <c r="W40" t="n">
-        <v>4134</v>
-      </c>
-      <c r="X40" t="inlineStr"/>
+        <v>496</v>
+      </c>
+      <c r="X40" t="n">
+        <v>8.01</v>
+      </c>
       <c r="Y40" t="n">
-        <v>39</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>258</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="n">
-        <v>30</v>
+        <v>391</v>
       </c>
       <c r="AB40" t="n">
-        <v>-1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AC40" t="n">
-        <v>6.38</v>
+        <v>19.9</v>
       </c>
       <c r="AD40" t="n">
-        <v>10.11</v>
+        <v>0.01</v>
       </c>
       <c r="AE40" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>61</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="n">
-        <v>190.9</v>
+        <v>20.42</v>
       </c>
       <c r="AH40" t="n">
-        <v>176.6</v>
+        <v>15.91</v>
       </c>
       <c r="AI40" t="n">
-        <v>27.8</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="AJ40" t="n">
-        <v>195.0500869565217</v>
+        <v>21.00741139152052</v>
       </c>
       <c r="AK40" t="n">
-        <v>-0.3</v>
+        <v>23.2</v>
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>22-09-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>25-09-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="AQ40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>56</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>54</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW40" t="n">
         <v>3</v>
       </c>
-      <c r="AR40" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>4</v>
-      </c>
       <c r="AX40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY40" t="n">
         <v>0</v>
@@ -9810,13 +9810,13 @@
         <v>0</v>
       </c>
       <c r="BA40" t="n">
-        <v>4486152</v>
+        <v>0</v>
       </c>
       <c r="BB40" t="n">
-        <v>4486152</v>
+        <v>4960333</v>
       </c>
       <c r="BC40" t="n">
-        <v>4486152</v>
+        <v>4960333</v>
       </c>
       <c r="BD40" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>0</v>
       </c>
       <c r="BO40" t="n">
-        <v>4486152</v>
+        <v>0</v>
       </c>
       <c r="BP40" t="n">
         <v>1</v>
@@ -9876,7 +9876,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -9896,13 +9896,13 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>28.46</v>
+        <v>27.07</v>
       </c>
       <c r="J41" t="n">
         <v>23.55</v>
       </c>
       <c r="K41" t="n">
-        <v>20.8</v>
+        <v>14.9</v>
       </c>
       <c r="L41" t="n">
         <v>68.34</v>
@@ -9939,10 +9939,10 @@
         </is>
       </c>
       <c r="V41" t="n">
-        <v>0.146</v>
+        <v>0.145</v>
       </c>
       <c r="W41" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="X41" t="n">
         <v>32</v>
@@ -9972,19 +9972,19 @@
         <v>14.87</v>
       </c>
       <c r="AG41" t="n">
-        <v>24.83</v>
+        <v>24.91</v>
       </c>
       <c r="AH41" t="n">
         <v>22.86</v>
       </c>
       <c r="AI41" t="n">
-        <v>22.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AJ41" t="n">
         <v>23.5472893358377</v>
       </c>
       <c r="AK41" t="n">
-        <v>20.9</v>
+        <v>15</v>
       </c>
       <c r="AL41" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
@@ -10108,7 +10108,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -10122,19 +10122,19 @@
         <v>15</v>
       </c>
       <c r="G42" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>365.05</v>
+        <v>379.05</v>
       </c>
       <c r="J42" t="n">
         <v>338.1</v>
       </c>
       <c r="K42" t="n">
-        <v>8</v>
+        <v>12.1</v>
       </c>
       <c r="L42" t="n">
         <v>66.73</v>
@@ -10171,13 +10171,13 @@
         </is>
       </c>
       <c r="V42" t="n">
-        <v>0.076</v>
+        <v>0.077</v>
       </c>
       <c r="W42" t="n">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="X42" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="Y42" t="n">
         <v>-8</v>
@@ -10204,19 +10204,19 @@
         <v>18</v>
       </c>
       <c r="AG42" t="n">
-        <v>370.99</v>
+        <v>371.04</v>
       </c>
       <c r="AH42" t="n">
-        <v>275.33</v>
+        <v>275.77</v>
       </c>
       <c r="AI42" t="n">
-        <v>60.2</v>
+        <v>63.1</v>
       </c>
       <c r="AJ42" t="n">
         <v>338.1</v>
       </c>
       <c r="AK42" t="n">
-        <v>8</v>
+        <v>12.1</v>
       </c>
       <c r="AL42" t="inlineStr">
         <is>
@@ -10360,13 +10360,13 @@
         <v>-1</v>
       </c>
       <c r="I43" t="n">
-        <v>189.25</v>
+        <v>201.02</v>
       </c>
       <c r="J43" t="n">
         <v>170.45</v>
       </c>
       <c r="K43" t="n">
-        <v>11</v>
+        <v>17.9</v>
       </c>
       <c r="L43" t="n">
         <v>67.54000000000001</v>
@@ -10403,13 +10403,13 @@
         </is>
       </c>
       <c r="V43" t="n">
-        <v>0.097</v>
+        <v>0.096</v>
       </c>
       <c r="W43" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="X43" t="n">
-        <v>28.4</v>
+        <v>28.7</v>
       </c>
       <c r="Y43" t="n">
         <v>24</v>
@@ -10436,19 +10436,19 @@
         <v>2.97</v>
       </c>
       <c r="AG43" t="n">
-        <v>182.38</v>
+        <v>183.05</v>
       </c>
       <c r="AH43" t="n">
-        <v>164.81</v>
+        <v>165.04</v>
       </c>
       <c r="AI43" t="n">
-        <v>31.2</v>
+        <v>36.5</v>
       </c>
       <c r="AJ43" t="n">
         <v>170.4518641810919</v>
       </c>
       <c r="AK43" t="n">
-        <v>11</v>
+        <v>17.9</v>
       </c>
       <c r="AL43" t="inlineStr">
         <is>
@@ -10592,13 +10592,13 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>616.2</v>
+        <v>615.35</v>
       </c>
       <c r="J44" t="n">
         <v>622.4400000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="L44" t="n">
         <v>74.02</v>
@@ -10635,10 +10635,10 @@
         </is>
       </c>
       <c r="V44" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
       <c r="W44" t="n">
-        <v>945</v>
+        <v>959</v>
       </c>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="n">
@@ -10666,19 +10666,19 @@
         <v>6</v>
       </c>
       <c r="AG44" t="n">
-        <v>599.9400000000001</v>
+        <v>600.3200000000001</v>
       </c>
       <c r="AH44" t="n">
-        <v>551.7</v>
+        <v>552.13</v>
       </c>
       <c r="AI44" t="n">
-        <v>22.1</v>
+        <v>22.9</v>
       </c>
       <c r="AJ44" t="n">
         <v>622.4351173945973</v>
       </c>
       <c r="AK44" t="n">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="AL44" t="inlineStr">
         <is>
@@ -10822,13 +10822,13 @@
         <v>-19</v>
       </c>
       <c r="I45" t="n">
-        <v>1752.2</v>
+        <v>1791.9</v>
       </c>
       <c r="J45" t="n">
         <v>1579.83</v>
       </c>
       <c r="K45" t="n">
-        <v>10.9</v>
+        <v>13.4</v>
       </c>
       <c r="L45" t="n">
         <v>67.55</v>
@@ -10868,7 +10868,7 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>3740</v>
+        <v>3742</v>
       </c>
       <c r="X45" t="n">
         <v>84.2</v>
@@ -10898,19 +10898,19 @@
         <v>27</v>
       </c>
       <c r="AG45" t="n">
-        <v>1676.07</v>
+        <v>1681.8</v>
       </c>
       <c r="AH45" t="n">
-        <v>1400.19</v>
+        <v>1402</v>
       </c>
       <c r="AI45" t="n">
-        <v>42.7</v>
+        <v>42.1</v>
       </c>
       <c r="AJ45" t="n">
         <v>1579.830529039607</v>
       </c>
       <c r="AK45" t="n">
-        <v>10.9</v>
+        <v>13.4</v>
       </c>
       <c r="AL45" t="inlineStr">
         <is>
@@ -11054,13 +11054,13 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>266.7</v>
+        <v>268</v>
       </c>
       <c r="J46" t="n">
         <v>278.98</v>
       </c>
       <c r="K46" t="n">
-        <v>-4.4</v>
+        <v>-3.9</v>
       </c>
       <c r="L46" t="n">
         <v>73.72</v>
@@ -11100,10 +11100,10 @@
         <v>0.006</v>
       </c>
       <c r="W46" t="n">
-        <v>4860</v>
+        <v>4868</v>
       </c>
       <c r="X46" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="Y46" t="n">
         <v>23</v>
@@ -11126,19 +11126,19 @@
       </c>
       <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="n">
-        <v>293.62</v>
+        <v>292.59</v>
       </c>
       <c r="AH46" t="n">
-        <v>310.37</v>
+        <v>310.13</v>
       </c>
       <c r="AI46" t="n">
-        <v>-14.4</v>
+        <v>-13.6</v>
       </c>
       <c r="AJ46" t="n">
         <v>278.9837</v>
       </c>
       <c r="AK46" t="n">
-        <v>-4.4</v>
+        <v>-3.9</v>
       </c>
       <c r="AL46" t="inlineStr">
         <is>
@@ -11282,13 +11282,13 @@
         <v>-18</v>
       </c>
       <c r="I47" t="n">
-        <v>1016.7</v>
+        <v>1012.5</v>
       </c>
       <c r="J47" t="n">
         <v>1157.18</v>
       </c>
       <c r="K47" t="n">
-        <v>-12.1</v>
+        <v>-12.5</v>
       </c>
       <c r="L47" t="n">
         <v>61.21</v>
@@ -11328,10 +11328,10 @@
         <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>102815</v>
+        <v>103386</v>
       </c>
       <c r="X47" t="n">
-        <v>29.6</v>
+        <v>29.8</v>
       </c>
       <c r="Y47" t="n">
         <v>18</v>
@@ -11358,19 +11358,19 @@
         <v>15</v>
       </c>
       <c r="AG47" t="n">
-        <v>1123.5</v>
+        <v>1121.87</v>
       </c>
       <c r="AH47" t="n">
-        <v>1136.78</v>
+        <v>1136.84</v>
       </c>
       <c r="AI47" t="n">
-        <v>-16.2</v>
+        <v>-15.6</v>
       </c>
       <c r="AJ47" t="n">
         <v>1157.177537688442</v>
       </c>
       <c r="AK47" t="n">
-        <v>-12.1</v>
+        <v>-12.5</v>
       </c>
       <c r="AL47" t="inlineStr">
         <is>
@@ -11514,13 +11514,13 @@
         <v>-1</v>
       </c>
       <c r="I48" t="n">
-        <v>101.24</v>
+        <v>100.78</v>
       </c>
       <c r="J48" t="n">
         <v>111.01</v>
       </c>
       <c r="K48" t="n">
-        <v>-8.800000000000001</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="L48" t="n">
         <v>73.48</v>
@@ -11557,13 +11557,13 @@
         </is>
       </c>
       <c r="V48" t="n">
-        <v>0.236</v>
+        <v>0.239</v>
       </c>
       <c r="W48" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="X48" t="n">
-        <v>22.6</v>
+        <v>22.4</v>
       </c>
       <c r="Y48" t="n">
         <v>21</v>
@@ -11590,19 +11590,19 @@
         <v>4.11</v>
       </c>
       <c r="AG48" t="n">
-        <v>111.57</v>
+        <v>111.38</v>
       </c>
       <c r="AH48" t="n">
-        <v>117.33</v>
+        <v>117.18</v>
       </c>
       <c r="AI48" t="n">
-        <v>-11.1</v>
+        <v>-11.7</v>
       </c>
       <c r="AJ48" t="n">
         <v>111.0077475247525</v>
       </c>
       <c r="AK48" t="n">
-        <v>-8.800000000000001</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
@@ -11798,13 +11798,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>83.67</v>
+        <v>84.18000000000001</v>
       </c>
       <c r="D2" t="n">
         <v>77.33</v>
       </c>
       <c r="E2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="F2" t="n">
         <v>61.32</v>
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>795.9</v>
+        <v>811</v>
       </c>
       <c r="D3" t="n">
         <v>819.08</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.8</v>
+        <v>-1</v>
       </c>
       <c r="F3" t="n">
         <v>73</v>
@@ -11868,13 +11868,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>296.55</v>
+        <v>308</v>
       </c>
       <c r="D4" t="n">
         <v>265.56</v>
       </c>
       <c r="E4" t="n">
-        <v>11.7</v>
+        <v>16</v>
       </c>
       <c r="F4" t="n">
         <v>64.63</v>
@@ -11894,66 +11894,66 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PKTEA</t>
+          <t>BMWVENTLTD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
+          <t>BMW VENTURES LIMITED</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>899</v>
+        <v>63.25</v>
       </c>
       <c r="D5" t="n">
-        <v>869.9299999999999</v>
+        <v>55.06</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3</v>
+        <v>14.9</v>
       </c>
       <c r="F5" t="n">
-        <v>61.71</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>5.19</v>
+        <v>2.9</v>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SIGIND</t>
+          <t>SRHHYPOLTD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Signet Industries Limited</t>
+          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>61.05</v>
+        <v>541.3</v>
       </c>
       <c r="D6" t="n">
-        <v>74.22</v>
+        <v>510.94</v>
       </c>
       <c r="E6" t="n">
-        <v>-17.7</v>
+        <v>5.9</v>
       </c>
       <c r="F6" t="n">
-        <v>72.56999999999999</v>
+        <v>61.84</v>
       </c>
       <c r="G6" t="n">
-        <v>2.01</v>
+        <v>3.06</v>
       </c>
       <c r="H6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -11964,175 +11964,175 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NURECA</t>
+          <t>SIGIND</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NURECA LIMITED</t>
+          <t>Signet Industries Limited</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>331.65</v>
+        <v>58.05</v>
       </c>
       <c r="D7" t="n">
-        <v>333.11</v>
+        <v>74.22</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4</v>
+        <v>-21.8</v>
       </c>
       <c r="F7" t="n">
-        <v>63.24</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>3.75</v>
+        <v>2.01</v>
       </c>
       <c r="H7" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>PKTEA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>THANGAMAYIL JEWELLERY LIMITED</t>
+          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4889.5</v>
+        <v>865.3</v>
       </c>
       <c r="D8" t="n">
-        <v>5198.76</v>
+        <v>869.9299999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.9</v>
+        <v>-0.5</v>
       </c>
       <c r="F8" t="n">
-        <v>67.16</v>
+        <v>61.71</v>
       </c>
       <c r="G8" t="n">
-        <v>7.21</v>
+        <v>5.19</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BMWVENTLTD</t>
+          <t>NURECA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BMW VENTURES LIMITED</t>
+          <t>NURECA LIMITED</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>57.95</v>
+        <v>331.4</v>
       </c>
       <c r="D9" t="n">
-        <v>55.06</v>
+        <v>333.11</v>
       </c>
       <c r="E9" t="n">
-        <v>5.2</v>
+        <v>-0.5</v>
       </c>
       <c r="F9" t="n">
-        <v>73.01000000000001</v>
+        <v>63.24</v>
       </c>
       <c r="G9" t="n">
-        <v>2.9</v>
+        <v>3.75</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>22-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DIAMONDYD</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Prataap Snacks Limited</t>
+          <t>THANGAMAYIL JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1049.4</v>
+        <v>4890.5</v>
       </c>
       <c r="D10" t="n">
-        <v>1175.33</v>
+        <v>5198.76</v>
       </c>
       <c r="E10" t="n">
-        <v>-10.7</v>
+        <v>-5.9</v>
       </c>
       <c r="F10" t="n">
-        <v>64.3</v>
+        <v>67.16</v>
       </c>
       <c r="G10" t="n">
-        <v>58.7</v>
+        <v>7.21</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SRHHYPOLTD</t>
+          <t>DIAMONDYD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
+          <t>Prataap Snacks Limited</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>533.85</v>
+        <v>1045.4</v>
       </c>
       <c r="D11" t="n">
-        <v>510.94</v>
+        <v>1175.33</v>
       </c>
       <c r="E11" t="n">
-        <v>4.5</v>
+        <v>-11.1</v>
       </c>
       <c r="F11" t="n">
-        <v>61.84</v>
+        <v>64.3</v>
       </c>
       <c r="G11" t="n">
-        <v>3.06</v>
+        <v>58.7</v>
       </c>
       <c r="H11" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
     </row>
@@ -12148,13 +12148,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>364.9</v>
+        <v>380.35</v>
       </c>
       <c r="D12" t="n">
         <v>217.8</v>
       </c>
       <c r="E12" t="n">
-        <v>67.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F12" t="n">
         <v>71.75</v>
@@ -12183,13 +12183,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>69.43000000000001</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="D13" t="n">
         <v>64.48999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>7.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F13" t="n">
         <v>64.29000000000001</v>
@@ -12218,13 +12218,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>99.25</v>
+        <v>99.56</v>
       </c>
       <c r="D14" t="n">
         <v>96.81999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="F14" t="n">
         <v>70.88</v>
@@ -12253,13 +12253,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>92.39</v>
+        <v>91.41</v>
       </c>
       <c r="D15" t="n">
         <v>75.68000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>22.1</v>
+        <v>20.8</v>
       </c>
       <c r="F15" t="n">
         <v>74.84999999999999</v>
@@ -12279,70 +12279,70 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SILVERTUC</t>
+          <t>CHEMBONDCH</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
+          <t>CHEMBOND CHEMICALS LIMITED</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>131.18</v>
+        <v>247.47</v>
       </c>
       <c r="D16" t="n">
-        <v>171.54</v>
+        <v>243.52</v>
       </c>
       <c r="E16" t="n">
-        <v>-23.5</v>
+        <v>1.6</v>
       </c>
       <c r="F16" t="n">
-        <v>74.59</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="G16" t="n">
         <v>1.11</v>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TAINWALCHM</t>
+          <t>SILVERTUC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
+          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>219.26</v>
+        <v>128.72</v>
       </c>
       <c r="D17" t="n">
-        <v>210.19</v>
+        <v>171.54</v>
       </c>
       <c r="E17" t="n">
-        <v>4.3</v>
+        <v>-25</v>
       </c>
       <c r="F17" t="n">
-        <v>67.04000000000001</v>
+        <v>74.59</v>
       </c>
       <c r="G17" t="n">
-        <v>0.62</v>
+        <v>1.11</v>
       </c>
       <c r="H17" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>28-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
     </row>
@@ -12358,13 +12358,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>133.9</v>
+        <v>132.22</v>
       </c>
       <c r="D18" t="n">
         <v>143.72</v>
       </c>
       <c r="E18" t="n">
-        <v>-6.8</v>
+        <v>-8</v>
       </c>
       <c r="F18" t="n">
         <v>63.69</v>
@@ -12384,35 +12384,35 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CHEMBONDCH</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CHEMBOND CHEMICALS LIMITED</t>
+          <t>OBCL LIMITED</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>220.86</v>
+        <v>55.56</v>
       </c>
       <c r="D19" t="n">
-        <v>243.52</v>
+        <v>54.07</v>
       </c>
       <c r="E19" t="n">
-        <v>-9.300000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="F19" t="n">
-        <v>67.65000000000001</v>
+        <v>67.23</v>
       </c>
       <c r="G19" t="n">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
     </row>
@@ -12428,13 +12428,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>471.9</v>
+        <v>470.2</v>
       </c>
       <c r="D20" t="n">
         <v>489.56</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.6</v>
+        <v>-4</v>
       </c>
       <c r="F20" t="n">
         <v>75</v>
@@ -12463,13 +12463,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>212.86</v>
+        <v>210.75</v>
       </c>
       <c r="D21" t="n">
         <v>232.74</v>
       </c>
       <c r="E21" t="n">
-        <v>-8.5</v>
+        <v>-9.4</v>
       </c>
       <c r="F21" t="n">
         <v>67.13</v>
@@ -12498,13 +12498,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>90.37</v>
+        <v>90.83</v>
       </c>
       <c r="D22" t="n">
         <v>68.68000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>31.6</v>
+        <v>32.3</v>
       </c>
       <c r="F22" t="n">
         <v>71.22</v>
@@ -12533,13 +12533,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>115.81</v>
+        <v>118.12</v>
       </c>
       <c r="D23" t="n">
         <v>132.2</v>
       </c>
       <c r="E23" t="n">
-        <v>-12.4</v>
+        <v>-10.7</v>
       </c>
       <c r="F23" t="n">
         <v>67.83</v>
@@ -12559,31 +12559,31 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STEL</t>
+          <t>TAINWALCHM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>STEL HOLDINGS LIMITED</t>
+          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>545.25</v>
+        <v>207.23</v>
       </c>
       <c r="D24" t="n">
-        <v>638.11</v>
+        <v>210.19</v>
       </c>
       <c r="E24" t="n">
-        <v>-14.6</v>
+        <v>-1.4</v>
       </c>
       <c r="F24" t="n">
-        <v>64.68000000000001</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>3.93</v>
+        <v>0.62</v>
       </c>
       <c r="H24" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -12594,136 +12594,136 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>WCIL</t>
+          <t>STEL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
+          <t>STEL HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>97.52</v>
+        <v>520.6</v>
       </c>
       <c r="D25" t="n">
-        <v>96.03</v>
+        <v>638.11</v>
       </c>
       <c r="E25" t="n">
-        <v>1.6</v>
+        <v>-18.4</v>
       </c>
       <c r="F25" t="n">
-        <v>71.89</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>2.6</v>
+        <v>3.93</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>28-09-2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GANESHCP</t>
+          <t>WCIL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
+          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>152.08</v>
+        <v>98.23</v>
       </c>
       <c r="D26" t="n">
-        <v>166</v>
+        <v>96.03</v>
       </c>
       <c r="E26" t="n">
-        <v>-8.4</v>
+        <v>2.3</v>
       </c>
       <c r="F26" t="n">
-        <v>64.08</v>
+        <v>71.89</v>
       </c>
       <c r="G26" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SINCLAIR</t>
+          <t>GANESHCP</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SINCLAIRS HOTELS LIMITED</t>
+          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>74.45999999999999</v>
+        <v>155.7</v>
       </c>
       <c r="D27" t="n">
-        <v>81.09999999999999</v>
+        <v>166</v>
       </c>
       <c r="E27" t="n">
-        <v>-8.199999999999999</v>
+        <v>-6.2</v>
       </c>
       <c r="F27" t="n">
-        <v>62.78</v>
+        <v>64.08</v>
       </c>
       <c r="G27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H27" t="n">
         <v>2</v>
       </c>
-      <c r="H27" t="n">
-        <v>8</v>
-      </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>SINCLAIR</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>OBCL LIMITED</t>
+          <t>SINCLAIRS HOTELS LIMITED</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>55.19</v>
+        <v>74.16</v>
       </c>
       <c r="D28" t="n">
-        <v>54.07</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>2.1</v>
+        <v>-8.6</v>
       </c>
       <c r="F28" t="n">
-        <v>67.23</v>
+        <v>62.78</v>
       </c>
       <c r="G28" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -12743,13 +12743,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>414.5</v>
+        <v>422.3</v>
       </c>
       <c r="D29" t="n">
         <v>417.34</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.7</v>
+        <v>1.2</v>
       </c>
       <c r="F29" t="n">
         <v>61.75</v>
@@ -12778,13 +12778,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>159.8</v>
+        <v>165.04</v>
       </c>
       <c r="D30" t="n">
         <v>174.27</v>
       </c>
       <c r="E30" t="n">
-        <v>-8.300000000000001</v>
+        <v>-5.3</v>
       </c>
       <c r="F30" t="n">
         <v>61.48</v>
@@ -12813,13 +12813,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>23.59</v>
+        <v>24.08</v>
       </c>
       <c r="D31" t="n">
         <v>27.53</v>
       </c>
       <c r="E31" t="n">
-        <v>-14.3</v>
+        <v>-12.5</v>
       </c>
       <c r="F31" t="n">
         <v>61.81</v>
@@ -12839,136 +12839,136 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DANGEE</t>
+          <t>TRUALT</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Dangee Dums Limited</t>
+          <t>TRUALT BIOENERGY LIMITED</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3.2</v>
+        <v>443.25</v>
       </c>
       <c r="D32" t="n">
-        <v>2.82</v>
+        <v>349.57</v>
       </c>
       <c r="E32" t="n">
-        <v>13.5</v>
+        <v>26.8</v>
       </c>
       <c r="F32" t="n">
-        <v>64.45</v>
+        <v>70.55</v>
       </c>
       <c r="G32" t="n">
-        <v>2.02</v>
+        <v>31.6</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>LAOPALA</t>
+          <t>AVONMORE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LA OPALA RG LIMITED</t>
+          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>154.76</v>
+        <v>12.76</v>
       </c>
       <c r="D33" t="n">
-        <v>159.62</v>
+        <v>12.86</v>
       </c>
       <c r="E33" t="n">
-        <v>-3</v>
+        <v>-0.8</v>
       </c>
       <c r="F33" t="n">
-        <v>65.64</v>
+        <v>69.12</v>
       </c>
       <c r="G33" t="n">
-        <v>3.99</v>
+        <v>2.35</v>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>17-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>LAOPALA</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ENVIRO INFRA ENGINEERS LIMITED</t>
+          <t>LA OPALA RG LIMITED</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>179.96</v>
+        <v>151.9</v>
       </c>
       <c r="D34" t="n">
-        <v>191.87</v>
+        <v>159.62</v>
       </c>
       <c r="E34" t="n">
-        <v>-6.2</v>
+        <v>-4.8</v>
       </c>
       <c r="F34" t="n">
-        <v>70.02</v>
+        <v>65.64</v>
       </c>
       <c r="G34" t="n">
-        <v>1.34</v>
+        <v>3.99</v>
       </c>
       <c r="H34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GOKUL</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
+          <t>ENVIRO INFRA ENGINEERS LIMITED</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>38.05</v>
+        <v>178.87</v>
       </c>
       <c r="D35" t="n">
-        <v>42.6</v>
+        <v>191.87</v>
       </c>
       <c r="E35" t="n">
-        <v>-10.7</v>
+        <v>-6.8</v>
       </c>
       <c r="F35" t="n">
-        <v>71.79000000000001</v>
+        <v>70.02</v>
       </c>
       <c r="G35" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="H35" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -12979,70 +12979,70 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AVONMORE</t>
+          <t>GOKUL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
+          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>12.3</v>
+        <v>38.04</v>
       </c>
       <c r="D36" t="n">
-        <v>12.86</v>
+        <v>42.6</v>
       </c>
       <c r="E36" t="n">
-        <v>-4.4</v>
+        <v>-10.7</v>
       </c>
       <c r="F36" t="n">
-        <v>69.12</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>2.35</v>
+        <v>1.4</v>
       </c>
       <c r="H36" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>DANGEE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TRUALT BIOENERGY LIMITED</t>
+          <t>Dangee Dums Limited</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>427.2</v>
+        <v>3.13</v>
       </c>
       <c r="D37" t="n">
-        <v>349.57</v>
+        <v>2.82</v>
       </c>
       <c r="E37" t="n">
-        <v>22.2</v>
+        <v>11</v>
       </c>
       <c r="F37" t="n">
-        <v>70.55</v>
+        <v>64.45</v>
       </c>
       <c r="G37" t="n">
-        <v>31.6</v>
+        <v>2.02</v>
       </c>
       <c r="H37" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
     </row>
@@ -13058,13 +13058,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>764.8</v>
+        <v>781.1</v>
       </c>
       <c r="D38" t="n">
         <v>726.25</v>
       </c>
       <c r="E38" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="F38" t="n">
         <v>71.92</v>
@@ -13084,70 +13084,70 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>INDIQUBE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>U. Y. Fincorp Limited</t>
+          <t>Indiqube Spaces Limited</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>24.76</v>
+        <v>191.7</v>
       </c>
       <c r="D39" t="n">
-        <v>21.01</v>
+        <v>195.05</v>
       </c>
       <c r="E39" t="n">
-        <v>17.8</v>
+        <v>-1.7</v>
       </c>
       <c r="F39" t="n">
-        <v>70.87</v>
+        <v>60.6</v>
       </c>
       <c r="G39" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="H39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>25-09-2026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>INDIQUBE</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Indiqube Spaces Limited</t>
+          <t>U. Y. Fincorp Limited</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>194.47</v>
+        <v>25.88</v>
       </c>
       <c r="D40" t="n">
-        <v>195.05</v>
+        <v>21.01</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.3</v>
+        <v>23.2</v>
       </c>
       <c r="F40" t="n">
-        <v>60.6</v>
+        <v>70.87</v>
       </c>
       <c r="G40" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="H40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>25-09-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
     </row>
@@ -13163,13 +13163,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>28.46</v>
+        <v>27.07</v>
       </c>
       <c r="D41" t="n">
         <v>23.55</v>
       </c>
       <c r="E41" t="n">
-        <v>20.8</v>
+        <v>14.9</v>
       </c>
       <c r="F41" t="n">
         <v>68.34</v>
@@ -13198,13 +13198,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>365.05</v>
+        <v>379.05</v>
       </c>
       <c r="D42" t="n">
         <v>338.1</v>
       </c>
       <c r="E42" t="n">
-        <v>8</v>
+        <v>12.1</v>
       </c>
       <c r="F42" t="n">
         <v>66.73</v>
@@ -13233,13 +13233,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>189.25</v>
+        <v>201.02</v>
       </c>
       <c r="D43" t="n">
         <v>170.45</v>
       </c>
       <c r="E43" t="n">
-        <v>11</v>
+        <v>17.9</v>
       </c>
       <c r="F43" t="n">
         <v>67.54000000000001</v>
@@ -13268,13 +13268,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>616.2</v>
+        <v>615.35</v>
       </c>
       <c r="D44" t="n">
         <v>622.4400000000001</v>
       </c>
       <c r="E44" t="n">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="F44" t="n">
         <v>74.02</v>
@@ -13303,13 +13303,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1752.2</v>
+        <v>1791.9</v>
       </c>
       <c r="D45" t="n">
         <v>1579.83</v>
       </c>
       <c r="E45" t="n">
-        <v>10.9</v>
+        <v>13.4</v>
       </c>
       <c r="F45" t="n">
         <v>67.55</v>
@@ -13338,13 +13338,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>266.7</v>
+        <v>268</v>
       </c>
       <c r="D46" t="n">
         <v>278.98</v>
       </c>
       <c r="E46" t="n">
-        <v>-4.4</v>
+        <v>-3.9</v>
       </c>
       <c r="F46" t="n">
         <v>73.72</v>
@@ -13373,13 +13373,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1016.7</v>
+        <v>1012.5</v>
       </c>
       <c r="D47" t="n">
         <v>1157.18</v>
       </c>
       <c r="E47" t="n">
-        <v>-12.1</v>
+        <v>-12.5</v>
       </c>
       <c r="F47" t="n">
         <v>61.21</v>
@@ -13408,13 +13408,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>101.24</v>
+        <v>100.78</v>
       </c>
       <c r="D48" t="n">
         <v>111.01</v>
       </c>
       <c r="E48" t="n">
-        <v>-8.800000000000001</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="F48" t="n">
         <v>73.48</v>
@@ -13464,7 +13464,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -13474,7 +13474,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -13484,7 +13484,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -13514,7 +13514,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -13544,7 +13544,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
